--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0CD55B-895E-4622-8EC8-698D1A239C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9159FAFE-E536-4E10-A680-45440C6EF58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Cadastro_Agentes" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="405">
   <si>
     <t>Realizado_por</t>
   </si>
@@ -1248,6 +1248,9 @@
   </si>
   <si>
     <t>HHA-FRISNE</t>
+  </si>
+  <si>
+    <t>HHA-LUTHA2</t>
   </si>
 </sst>
 </file>
@@ -1340,7 +1343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1377,7 +1380,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1692,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD67F592-4C9C-4072-A458-8E5A8476F407}">
-  <dimension ref="A1:D365"/>
+  <dimension ref="A1:D366"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.77734375" customWidth="1"/>
@@ -5923,7 +5925,7 @@
       <c r="C302" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D302" s="16">
+      <c r="D302" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5937,7 +5939,7 @@
       <c r="C303" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D303" s="16">
+      <c r="D303" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5951,7 +5953,7 @@
       <c r="C304" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D304" s="16">
+      <c r="D304" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5965,7 +5967,7 @@
       <c r="C305" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D305" s="16">
+      <c r="D305" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5979,7 +5981,7 @@
       <c r="C306" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D306" s="16">
+      <c r="D306" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5993,7 +5995,7 @@
       <c r="C307" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D307" s="16">
+      <c r="D307" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6007,7 +6009,7 @@
       <c r="C308" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D308" s="16">
+      <c r="D308" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6021,7 +6023,7 @@
       <c r="C309" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D309" s="16">
+      <c r="D309" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6035,7 +6037,7 @@
       <c r="C310" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D310" s="16">
+      <c r="D310" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6049,7 +6051,7 @@
       <c r="C311" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D311" s="16">
+      <c r="D311" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6063,7 +6065,7 @@
       <c r="C312" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D312" s="16">
+      <c r="D312" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6077,7 +6079,7 @@
       <c r="C313" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D313" s="16">
+      <c r="D313" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6091,7 +6093,7 @@
       <c r="C314" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D314" s="16">
+      <c r="D314" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6105,7 +6107,7 @@
       <c r="C315" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D315" s="16">
+      <c r="D315" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6119,7 +6121,7 @@
       <c r="C316" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D316" s="16">
+      <c r="D316" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6133,7 +6135,7 @@
       <c r="C317" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D317" s="16">
+      <c r="D317" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6147,7 +6149,7 @@
       <c r="C318" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D318" s="16">
+      <c r="D318" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6161,7 +6163,7 @@
       <c r="C319" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D319" s="16">
+      <c r="D319" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6175,7 +6177,7 @@
       <c r="C320" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D320" s="16">
+      <c r="D320" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6189,7 +6191,7 @@
       <c r="C321" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D321" s="16">
+      <c r="D321" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6203,7 +6205,7 @@
       <c r="C322" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D322" s="16">
+      <c r="D322" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6217,7 +6219,7 @@
       <c r="C323" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D323" s="16">
+      <c r="D323" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6231,7 +6233,7 @@
       <c r="C324" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D324" s="16">
+      <c r="D324" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6245,7 +6247,7 @@
       <c r="C325" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D325" s="16">
+      <c r="D325" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6259,7 +6261,7 @@
       <c r="C326" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D326" s="16">
+      <c r="D326" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6273,7 +6275,7 @@
       <c r="C327" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D327" s="16">
+      <c r="D327" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6287,7 +6289,7 @@
       <c r="C328" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D328" s="16">
+      <c r="D328" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6301,7 +6303,7 @@
       <c r="C329" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D329" s="16">
+      <c r="D329" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6315,7 +6317,7 @@
       <c r="C330" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D330" s="16">
+      <c r="D330" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6329,7 +6331,7 @@
       <c r="C331" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D331" s="16">
+      <c r="D331" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6343,7 +6345,7 @@
       <c r="C332" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D332" s="16">
+      <c r="D332" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6357,7 +6359,7 @@
       <c r="C333" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D333" s="16">
+      <c r="D333" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6371,7 +6373,7 @@
       <c r="C334" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D334" s="16">
+      <c r="D334" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6385,7 +6387,7 @@
       <c r="C335" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D335" s="16">
+      <c r="D335" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6399,7 +6401,7 @@
       <c r="C336" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D336" s="16">
+      <c r="D336" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6413,7 +6415,7 @@
       <c r="C337" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D337" s="16">
+      <c r="D337" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6427,27 +6429,27 @@
       <c r="C338" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D338" s="16">
+      <c r="D338" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="B339" s="13">
-        <v>20</v>
+        <v>404</v>
+      </c>
+      <c r="B339" s="14">
+        <v>40</v>
       </c>
       <c r="C339" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D339" s="16">
+      <c r="D339" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" s="10" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B340" s="13">
         <v>20</v>
@@ -6455,13 +6457,13 @@
       <c r="C340" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D340" s="16">
+      <c r="D340" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" s="10" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B341" s="13">
         <v>20</v>
@@ -6469,13 +6471,13 @@
       <c r="C341" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D341" s="16">
+      <c r="D341" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" s="10" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B342" s="13">
         <v>20</v>
@@ -6483,13 +6485,13 @@
       <c r="C342" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D342" s="16">
+      <c r="D342" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" s="10" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="B343" s="13">
         <v>20</v>
@@ -6497,13 +6499,13 @@
       <c r="C343" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D343" s="16">
+      <c r="D343" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" s="10" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="B344" s="13">
         <v>20</v>
@@ -6511,13 +6513,13 @@
       <c r="C344" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D344" s="16">
+      <c r="D344" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" s="10" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="B345" s="13">
         <v>20</v>
@@ -6525,13 +6527,13 @@
       <c r="C345" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D345" s="16">
+      <c r="D345" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" s="10" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="B346" s="13">
         <v>20</v>
@@ -6539,13 +6541,13 @@
       <c r="C346" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D346" s="16">
+      <c r="D346" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" s="10" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B347" s="13">
         <v>20</v>
@@ -6553,13 +6555,13 @@
       <c r="C347" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D347" s="16">
+      <c r="D347" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" s="10" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B348" s="13">
         <v>20</v>
@@ -6567,13 +6569,13 @@
       <c r="C348" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D348" s="16">
+      <c r="D348" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" s="10" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="B349" s="13">
         <v>20</v>
@@ -6581,13 +6583,13 @@
       <c r="C349" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D349" s="16">
+      <c r="D349" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" s="10" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B350" s="13">
         <v>20</v>
@@ -6595,13 +6597,13 @@
       <c r="C350" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D350" s="16">
+      <c r="D350" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" s="10" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="B351" s="13">
         <v>20</v>
@@ -6609,13 +6611,13 @@
       <c r="C351" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D351" s="16">
+      <c r="D351" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" s="10" t="s">
-        <v>398</v>
+        <v>232</v>
       </c>
       <c r="B352" s="13">
         <v>20</v>
@@ -6623,13 +6625,13 @@
       <c r="C352" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D352" s="16">
+      <c r="D352" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" s="10" t="s">
-        <v>259</v>
+        <v>398</v>
       </c>
       <c r="B353" s="13">
         <v>20</v>
@@ -6637,13 +6639,13 @@
       <c r="C353" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D353" s="16">
+      <c r="D353" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" s="10" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B354" s="13">
         <v>20</v>
@@ -6651,13 +6653,13 @@
       <c r="C354" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D354" s="16">
+      <c r="D354" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" s="10" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="B355" s="13">
         <v>20</v>
@@ -6665,13 +6667,13 @@
       <c r="C355" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D355" s="16">
+      <c r="D355" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B356" s="13">
         <v>20</v>
@@ -6679,13 +6681,13 @@
       <c r="C356" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D356" s="16">
+      <c r="D356" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" s="10" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="B357" s="13">
         <v>20</v>
@@ -6693,13 +6695,13 @@
       <c r="C357" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D357" s="16">
+      <c r="D357" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" s="10" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B358" s="13">
         <v>20</v>
@@ -6707,13 +6709,13 @@
       <c r="C358" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D358" s="16">
+      <c r="D358" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B359" s="13">
         <v>20</v>
@@ -6721,13 +6723,13 @@
       <c r="C359" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D359" s="16">
+      <c r="D359" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" s="10" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B360" s="13">
         <v>20</v>
@@ -6735,13 +6737,13 @@
       <c r="C360" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D360" s="16">
+      <c r="D360" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" s="10" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B361" s="13">
         <v>20</v>
@@ -6749,13 +6751,13 @@
       <c r="C361" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D361" s="16">
+      <c r="D361" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B362" s="13">
         <v>20</v>
@@ -6763,27 +6765,27 @@
       <c r="C362" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D362" s="16">
+      <c r="D362" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" s="10" t="s">
-        <v>399</v>
+        <v>260</v>
       </c>
       <c r="B363" s="13">
         <v>20</v>
       </c>
       <c r="C363" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="D363" s="16">
+        <v>230</v>
+      </c>
+      <c r="D363" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B364" s="13">
         <v>20</v>
@@ -6791,13 +6793,13 @@
       <c r="C364" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="D364" s="16">
+      <c r="D364" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B365" s="13">
         <v>20</v>
@@ -6805,7 +6807,21 @@
       <c r="C365" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="D365" s="16">
+      <c r="D365" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A366" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B366" s="13">
+        <v>20</v>
+      </c>
+      <c r="C366" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D366" s="8">
         <v>0</v>
       </c>
     </row>

--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFADF22-D90F-4597-8E9F-6C183E28D337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EFA9BF-E65E-4152-9005-20C7FABDB90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
@@ -1328,9 +1328,6 @@
     <t>HHA-SALA CONSOLIDADO</t>
   </si>
   <si>
-    <t>Coluna1</t>
-  </si>
-  <si>
     <t>HHR-LENOT ONSOLIDADO</t>
   </si>
   <si>
@@ -1338,6 +1335,9 @@
   </si>
   <si>
     <t>R-VALLE CONSOLIDADO</t>
+  </si>
+  <si>
+    <t>Nome_Consolidado</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1465,9 +1465,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1621,7 +1618,7 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A4BD7FC1-F519-41FB-AA5E-E1B407B65298}" name="Realizado_por" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{AED2FF8D-3E1F-4E87-9C73-50549E264588}" name="Coluna1" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{AED2FF8D-3E1F-4E87-9C73-50549E264588}" name="Nome_Consolidado" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{62BC3A25-49A1-404A-9F26-ACD97EA076DC}" name="ID_Pacote_Comissao" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{386F9946-EC34-43A0-BE67-072922F298E5}" name="Comercial" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{E6264106-2D73-4EE8-9FD5-C93FD06484FF}" name="Regra_Fixo_Comercial" dataDxfId="0"/>
@@ -1941,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>1</v>
@@ -2705,7 +2702,7 @@
       <c r="A46" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="10" t="s">
         <v>408</v>
       </c>
       <c r="C46" s="13">
@@ -2722,7 +2719,7 @@
       <c r="A47" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="10" t="s">
         <v>408</v>
       </c>
       <c r="C47" s="13">
@@ -2739,7 +2736,7 @@
       <c r="A48" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="10" t="s">
         <v>108</v>
       </c>
       <c r="C48" s="13">
@@ -2756,7 +2753,7 @@
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="10" t="s">
         <v>87</v>
       </c>
       <c r="C49" s="13">
@@ -4897,7 +4894,7 @@
         <v>46</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C175" s="13">
         <v>20</v>
@@ -4914,7 +4911,7 @@
         <v>359</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C176" s="13">
         <v>20</v>
@@ -7855,7 +7852,7 @@
         <v>380</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C349" s="13">
         <v>20</v>
@@ -7872,7 +7869,7 @@
         <v>56</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C350" s="13">
         <v>20</v>
@@ -7957,7 +7954,7 @@
         <v>35</v>
       </c>
       <c r="B355" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C355" s="13">
         <v>20</v>
@@ -7974,7 +7971,7 @@
         <v>373</v>
       </c>
       <c r="B356" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C356" s="13">
         <v>20</v>
@@ -7991,7 +7988,7 @@
         <v>374</v>
       </c>
       <c r="B357" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C357" s="13">
         <v>20</v>
@@ -8008,7 +8005,7 @@
         <v>395</v>
       </c>
       <c r="B358" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C358" s="13">
         <v>20</v>

--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EFA9BF-E65E-4152-9005-20C7FABDB90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65230E5-B2C9-4699-B60E-AA07B6CAEC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="434">
   <si>
     <t>Realizado_por</t>
   </si>
@@ -1611,10 +1611,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E367" totalsRowShown="0">
-  <autoFilter ref="A1:E367" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E367">
-    <sortCondition ref="A1:A367"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E366" totalsRowShown="0">
+  <autoFilter ref="A1:E366" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E366">
+    <sortCondition ref="A1:A366"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A4BD7FC1-F519-41FB-AA5E-E1B407B65298}" name="Realizado_por" dataDxfId="4"/>
@@ -1924,7 +1924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD67F592-4C9C-4072-A458-8E5A8476F407}">
-  <dimension ref="A1:E366"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="53.77734375" customWidth="1"/>
@@ -3608,52 +3608,52 @@
         <v>20</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E99" s="11">
+        <v>230</v>
+      </c>
+      <c r="E99" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
-        <v>161</v>
+        <v>306</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>161</v>
+        <v>306</v>
       </c>
       <c r="C100" s="13">
         <v>20</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>230</v>
+        <v>114</v>
       </c>
       <c r="E100" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="C101" s="13">
         <v>20</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>114</v>
+        <v>230</v>
       </c>
       <c r="E101" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C102" s="13">
         <v>20</v>
@@ -3667,10 +3667,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C103" s="13">
         <v>20</v>
@@ -3684,10 +3684,10 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="C104" s="13">
         <v>20</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="C105" s="13">
         <v>20</v>
@@ -3718,10 +3718,10 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="C106" s="13">
         <v>20</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C107" s="13">
         <v>20</v>
@@ -3752,10 +3752,10 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="C108" s="13">
         <v>20</v>
@@ -3769,10 +3769,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C109" s="13">
         <v>20</v>
@@ -3786,10 +3786,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C110" s="13">
         <v>20</v>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="C111" s="13">
         <v>20</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="C112" s="13">
         <v>20</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="C113" s="13">
         <v>20</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="C114" s="13">
         <v>20</v>
@@ -3866,15 +3866,15 @@
         <v>230</v>
       </c>
       <c r="E114" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
-        <v>113</v>
+        <v>233</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>113</v>
+        <v>233</v>
       </c>
       <c r="C115" s="13">
         <v>20</v>
@@ -3883,18 +3883,18 @@
         <v>230</v>
       </c>
       <c r="E115" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
-        <v>233</v>
+        <v>404</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="C116" s="13">
-        <v>20</v>
+        <v>428</v>
+      </c>
+      <c r="C116" s="14">
+        <v>40</v>
       </c>
       <c r="D116" s="9" t="s">
         <v>230</v>
@@ -3905,7 +3905,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
-        <v>404</v>
+        <v>229</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>428</v>
@@ -3922,13 +3922,13 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="10" t="s">
-        <v>229</v>
+        <v>286</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="C118" s="14">
-        <v>40</v>
+        <v>286</v>
+      </c>
+      <c r="C118" s="13">
+        <v>20</v>
       </c>
       <c r="D118" s="9" t="s">
         <v>230</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="10" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C119" s="13">
         <v>20</v>
@@ -3956,10 +3956,10 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="C120" s="13">
         <v>20</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C121" s="13">
         <v>20</v>
@@ -3990,27 +3990,27 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
-        <v>246</v>
+        <v>333</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>246</v>
+        <v>414</v>
       </c>
       <c r="C122" s="13">
         <v>20</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="E122" s="8">
+        <v>328</v>
+      </c>
+      <c r="E122" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
-        <v>333</v>
+        <v>187</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C123" s="13">
         <v>20</v>
@@ -4024,44 +4024,44 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="10" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>413</v>
+        <v>130</v>
       </c>
       <c r="C124" s="13">
         <v>20</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E124" s="11">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="E124" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="10" t="s">
-        <v>130</v>
+        <v>264</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>130</v>
+        <v>264</v>
       </c>
       <c r="C125" s="13">
         <v>20</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>114</v>
+        <v>230</v>
       </c>
       <c r="E125" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="10" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="C126" s="13">
         <v>20</v>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="10" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="C127" s="13">
         <v>20</v>
@@ -4092,44 +4092,44 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="10" t="s">
-        <v>287</v>
+        <v>349</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>287</v>
+        <v>349</v>
       </c>
       <c r="C128" s="13">
         <v>20</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="E128" s="8">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="10" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="C129" s="13">
         <v>20</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="E129" s="8">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="10" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C130" s="13">
         <v>20</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="10" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C131" s="13">
         <v>20</v>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="C132" s="13">
         <v>20</v>
@@ -4177,10 +4177,10 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="10" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C133" s="13">
         <v>20</v>
@@ -4194,10 +4194,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="10" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>262</v>
+        <v>429</v>
       </c>
       <c r="C134" s="13">
         <v>20</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="10" t="s">
-        <v>232</v>
+        <v>398</v>
       </c>
       <c r="B135" s="10" t="s">
         <v>429</v>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="10" t="s">
-        <v>398</v>
+        <v>259</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>429</v>
+        <v>259</v>
       </c>
       <c r="C136" s="13">
         <v>20</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="10" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="C137" s="13">
         <v>20</v>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="10" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="C138" s="13">
         <v>20</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C139" s="13">
         <v>20</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="10" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="C140" s="13">
         <v>20</v>
@@ -4313,10 +4313,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="10" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C141" s="13">
         <v>20</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C142" s="13">
         <v>20</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="10" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C143" s="13">
         <v>20</v>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="10" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C144" s="13">
         <v>20</v>
@@ -4381,10 +4381,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C145" s="13">
         <v>20</v>
@@ -4398,27 +4398,27 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="10" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="C146" s="13">
         <v>20</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="E146" s="8">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C147" s="13">
         <v>20</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C148" s="13">
         <v>20</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="10" t="s">
-        <v>352</v>
+        <v>75</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>352</v>
+        <v>75</v>
       </c>
       <c r="C149" s="13">
         <v>20</v>
@@ -4466,10 +4466,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="10" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C150" s="13">
         <v>20</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="10" t="s">
-        <v>55</v>
+        <v>353</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>55</v>
+        <v>420</v>
       </c>
       <c r="C151" s="13">
         <v>20</v>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="10" t="s">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>420</v>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="10" t="s">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>420</v>
+        <v>354</v>
       </c>
       <c r="C153" s="13">
         <v>20</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C154" s="13">
         <v>20</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="10" t="s">
-        <v>355</v>
+        <v>42</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>355</v>
+        <v>42</v>
       </c>
       <c r="C155" s="13">
         <v>20</v>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C156" s="13">
         <v>20</v>
@@ -4585,10 +4585,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C157" s="13">
         <v>20</v>
@@ -4602,10 +4602,10 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C158" s="13">
         <v>20</v>
@@ -4619,10 +4619,10 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="10" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C159" s="13">
         <v>20</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C160" s="13">
         <v>20</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="10" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C161" s="13">
         <v>20</v>
@@ -4670,10 +4670,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="10" t="s">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>59</v>
+        <v>421</v>
       </c>
       <c r="C162" s="13">
         <v>20</v>
@@ -4687,7 +4687,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="10" t="s">
-        <v>356</v>
+        <v>63</v>
       </c>
       <c r="B163" s="10" t="s">
         <v>421</v>
@@ -4704,10 +4704,10 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>421</v>
+        <v>60</v>
       </c>
       <c r="C164" s="13">
         <v>20</v>
@@ -4721,10 +4721,10 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="10" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C165" s="13">
         <v>20</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="10" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C166" s="13">
         <v>20</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="10" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="C167" s="13">
         <v>20</v>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="10" t="s">
-        <v>26</v>
+        <v>383</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>26</v>
+        <v>383</v>
       </c>
       <c r="C168" s="13">
         <v>20</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="10" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="C169" s="13">
         <v>20</v>
@@ -4806,10 +4806,10 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="10" t="s">
-        <v>357</v>
+        <v>64</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>357</v>
+        <v>64</v>
       </c>
       <c r="C170" s="13">
         <v>20</v>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="10" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C171" s="13">
         <v>20</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="10" t="s">
-        <v>32</v>
+        <v>358</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>32</v>
+        <v>358</v>
       </c>
       <c r="C172" s="13">
         <v>20</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="10" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="C173" s="13">
         <v>20</v>
@@ -4874,10 +4874,10 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="10" t="s">
-        <v>387</v>
+        <v>46</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
       <c r="C174" s="13">
         <v>20</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="10" t="s">
-        <v>46</v>
+        <v>359</v>
       </c>
       <c r="B175" s="10" t="s">
         <v>430</v>
@@ -4908,10 +4908,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="10" t="s">
-        <v>359</v>
+        <v>25</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C176" s="13">
         <v>20</v>
@@ -4925,7 +4925,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="10" t="s">
-        <v>25</v>
+        <v>360</v>
       </c>
       <c r="B177" s="10" t="s">
         <v>422</v>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>422</v>
+        <v>361</v>
       </c>
       <c r="C178" s="13">
         <v>20</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="10" t="s">
-        <v>361</v>
+        <v>76</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>361</v>
+        <v>76</v>
       </c>
       <c r="C179" s="13">
         <v>20</v>
@@ -4976,10 +4976,10 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="10" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C180" s="13">
         <v>20</v>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="10" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="C181" s="13">
         <v>20</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="10" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C182" s="13">
         <v>20</v>
@@ -5027,10 +5027,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C183" s="13">
         <v>20</v>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="10" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C184" s="13">
         <v>20</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="10" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C185" s="13">
         <v>20</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="10" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C186" s="13">
         <v>20</v>
@@ -5095,10 +5095,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="10" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C187" s="13">
         <v>20</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C188" s="13">
         <v>20</v>
@@ -5129,10 +5129,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="10" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C189" s="13">
         <v>20</v>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="10" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C190" s="13">
         <v>20</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="10" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C191" s="13">
         <v>20</v>
@@ -5180,10 +5180,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="10" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C192" s="13">
         <v>20</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="10" t="s">
-        <v>50</v>
+        <v>362</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>50</v>
+        <v>423</v>
       </c>
       <c r="C193" s="13">
         <v>20</v>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="10" t="s">
-        <v>362</v>
+        <v>39</v>
       </c>
       <c r="B194" s="10" t="s">
         <v>423</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="10" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>423</v>
+        <v>27</v>
       </c>
       <c r="C195" s="13">
         <v>20</v>
@@ -5248,27 +5248,27 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="10" t="s">
-        <v>27</v>
+        <v>195</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>27</v>
+        <v>195</v>
       </c>
       <c r="C196" s="13">
         <v>20</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E196" s="8">
-        <v>0.75</v>
+        <v>328</v>
+      </c>
+      <c r="E196" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="10" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C197" s="13">
         <v>20</v>
@@ -5282,10 +5282,10 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="C198" s="13">
         <v>20</v>
@@ -5299,27 +5299,27 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="10" t="s">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="C199" s="13">
         <v>20</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E199" s="11">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="E199" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="10" t="s">
-        <v>121</v>
+        <v>307</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>121</v>
+        <v>307</v>
       </c>
       <c r="C200" s="13">
         <v>20</v>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="10" t="s">
-        <v>307</v>
+        <v>116</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>307</v>
+        <v>116</v>
       </c>
       <c r="C201" s="13">
         <v>20</v>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="10" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C202" s="13">
         <v>20</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="10" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C203" s="13">
         <v>20</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="10" t="s">
-        <v>119</v>
+        <v>308</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>119</v>
+        <v>405</v>
       </c>
       <c r="C204" s="13">
         <v>20</v>
@@ -5401,7 +5401,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="10" t="s">
-        <v>308</v>
+        <v>115</v>
       </c>
       <c r="B205" s="10" t="s">
         <v>405</v>
@@ -5418,10 +5418,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="10" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>405</v>
+        <v>128</v>
       </c>
       <c r="C206" s="13">
         <v>20</v>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C207" s="13">
         <v>20</v>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C208" s="13">
         <v>20</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="10" t="s">
-        <v>133</v>
+        <v>309</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>133</v>
+        <v>309</v>
       </c>
       <c r="C209" s="13">
         <v>20</v>
@@ -5486,10 +5486,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="10" t="s">
-        <v>309</v>
+        <v>124</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>309</v>
+        <v>124</v>
       </c>
       <c r="C210" s="13">
         <v>20</v>
@@ -5503,10 +5503,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="10" t="s">
-        <v>124</v>
+        <v>310</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="C211" s="13">
         <v>20</v>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>406</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="10" t="s">
-        <v>311</v>
+        <v>125</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>406</v>
+        <v>125</v>
       </c>
       <c r="C213" s="13">
         <v>20</v>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C214" s="13">
         <v>20</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C215" s="13">
         <v>20</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="10" t="s">
-        <v>126</v>
+        <v>312</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>126</v>
+        <v>312</v>
       </c>
       <c r="C216" s="13">
         <v>20</v>
@@ -5605,10 +5605,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="10" t="s">
-        <v>312</v>
+        <v>132</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>312</v>
+        <v>132</v>
       </c>
       <c r="C217" s="13">
         <v>20</v>
@@ -5622,10 +5622,10 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="10" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C218" s="13">
         <v>20</v>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C219" s="13">
         <v>20</v>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="10" t="s">
-        <v>123</v>
+        <v>313</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>123</v>
+        <v>313</v>
       </c>
       <c r="C220" s="13">
         <v>20</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C221" s="13">
         <v>20</v>
@@ -5690,10 +5690,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="10" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C222" s="13">
         <v>20</v>
@@ -5707,10 +5707,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="10" t="s">
-        <v>120</v>
+        <v>315</v>
       </c>
       <c r="B223" s="10" t="s">
-        <v>120</v>
+        <v>315</v>
       </c>
       <c r="C223" s="13">
         <v>20</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="10" t="s">
-        <v>315</v>
+        <v>118</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>315</v>
+        <v>118</v>
       </c>
       <c r="C224" s="13">
         <v>20</v>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C225" s="13">
         <v>20</v>
@@ -5758,27 +5758,27 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="10" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="C226" s="13">
         <v>20</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E226" s="8">
-        <v>1</v>
+        <v>328</v>
+      </c>
+      <c r="E226" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="10" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="C227" s="13">
         <v>20</v>
@@ -5792,10 +5792,10 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="10" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="C228" s="13">
         <v>20</v>
@@ -5809,10 +5809,10 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="10" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="C229" s="13">
         <v>20</v>
@@ -5826,10 +5826,10 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="10" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="C230" s="13">
         <v>20</v>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C231" s="13">
         <v>20</v>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="10" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C232" s="13">
         <v>20</v>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="10" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C233" s="13">
         <v>20</v>
@@ -5894,10 +5894,10 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="10" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="C234" s="13">
         <v>20</v>
@@ -5911,10 +5911,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="10" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="C235" s="13">
         <v>20</v>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="10" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="C236" s="13">
         <v>20</v>
@@ -5945,10 +5945,10 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="10" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="C237" s="13">
         <v>20</v>
@@ -5962,10 +5962,10 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="10" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C238" s="13">
         <v>20</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="10" t="s">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="C239" s="13">
         <v>20</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="10" t="s">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="C240" s="13">
         <v>20</v>
@@ -6013,10 +6013,10 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="10" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C241" s="13">
         <v>20</v>
@@ -6030,10 +6030,10 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="10" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C242" s="13">
         <v>20</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C243" s="13">
         <v>20</v>
@@ -6063,25 +6063,25 @@
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A244" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B244" s="10" t="s">
-        <v>172</v>
+      <c r="A244" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B244" s="15" t="s">
+        <v>411</v>
       </c>
       <c r="C244" s="13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D244" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E244" s="11">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="E244" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A245" s="15" t="s">
-        <v>326</v>
+      <c r="A245" s="10" t="s">
+        <v>288</v>
       </c>
       <c r="B245" s="15" t="s">
         <v>411</v>
@@ -6098,27 +6098,27 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="B246" s="15" t="s">
-        <v>411</v>
+        <v>153</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="C246" s="13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D246" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E246" s="8">
-        <v>1</v>
+        <v>328</v>
+      </c>
+      <c r="E246" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="10" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C247" s="13">
         <v>20</v>
@@ -6132,10 +6132,10 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="10" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="C248" s="13">
         <v>20</v>
@@ -6149,10 +6149,10 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="10" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C249" s="13">
         <v>20</v>
@@ -6166,10 +6166,10 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="10" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="C250" s="13">
         <v>20</v>
@@ -6183,10 +6183,10 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="10" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C251" s="13">
         <v>20</v>
@@ -6200,10 +6200,10 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C252" s="13">
         <v>20</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="10" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="C253" s="13">
         <v>20</v>
@@ -6234,10 +6234,10 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="10" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C254" s="13">
         <v>20</v>
@@ -6251,10 +6251,10 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="10" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="C255" s="13">
         <v>20</v>
@@ -6268,10 +6268,10 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="10" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="C256" s="13">
         <v>20</v>
@@ -6285,13 +6285,13 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="10" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C257" s="13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D257" s="9" t="s">
         <v>328</v>
@@ -6302,10 +6302,10 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="10" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="C258" s="13">
         <v>40</v>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C259" s="13">
         <v>40</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C260" s="13">
         <v>40</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="10" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C261" s="13">
         <v>40</v>
@@ -6370,10 +6370,10 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="10" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="C262" s="13">
         <v>40</v>
@@ -6387,10 +6387,10 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="10" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C263" s="13">
         <v>40</v>
@@ -6404,13 +6404,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="10" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C264" s="13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D264" s="9" t="s">
         <v>328</v>
@@ -6421,10 +6421,10 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="10" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="C265" s="13">
         <v>20</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="10" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C266" s="13">
         <v>20</v>
@@ -6455,10 +6455,10 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="10" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="C267" s="13">
         <v>20</v>
@@ -6472,10 +6472,10 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="10" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="C268" s="13">
         <v>20</v>
@@ -6489,10 +6489,10 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="10" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C269" s="13">
         <v>20</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="10" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C270" s="13">
         <v>20</v>
@@ -6523,10 +6523,10 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C271" s="13">
         <v>20</v>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="10" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C272" s="13">
         <v>20</v>
@@ -6557,10 +6557,10 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="10" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="C273" s="13">
         <v>20</v>
@@ -6574,10 +6574,10 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="10" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="C274" s="13">
         <v>20</v>
@@ -6591,10 +6591,10 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="10" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="C275" s="13">
         <v>20</v>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="10" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C276" s="13">
         <v>20</v>
@@ -6625,10 +6625,10 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="10" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="C277" s="13">
         <v>20</v>
@@ -6642,10 +6642,10 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="10" t="s">
-        <v>136</v>
+        <v>220</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>136</v>
+        <v>220</v>
       </c>
       <c r="C278" s="13">
         <v>20</v>
@@ -6659,10 +6659,10 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="10" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="C279" s="13">
         <v>20</v>
@@ -6676,10 +6676,10 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="10" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C280" s="13">
         <v>20</v>
@@ -6693,10 +6693,10 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="10" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="C281" s="13">
         <v>20</v>
@@ -6710,10 +6710,10 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="10" t="s">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="C282" s="13">
         <v>20</v>
@@ -6727,10 +6727,10 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="10" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="C283" s="13">
         <v>20</v>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="10" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C284" s="13">
         <v>20</v>
@@ -6761,10 +6761,10 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="10" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>174</v>
+        <v>412</v>
       </c>
       <c r="C285" s="13">
         <v>20</v>
@@ -6778,7 +6778,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="10" t="s">
-        <v>138</v>
+        <v>331</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>412</v>
@@ -6795,7 +6795,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B287" s="10" t="s">
         <v>412</v>
@@ -6812,7 +6812,7 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>412</v>
@@ -6829,7 +6829,7 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B289" s="10" t="s">
         <v>412</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="10" t="s">
-        <v>330</v>
+        <v>185</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>412</v>
+        <v>185</v>
       </c>
       <c r="C290" s="13">
         <v>20</v>
@@ -6863,10 +6863,10 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="10" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="C291" s="13">
         <v>20</v>
@@ -6880,10 +6880,10 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C292" s="13">
         <v>20</v>
@@ -6897,10 +6897,10 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B293" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C293" s="13">
         <v>20</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="10" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="C294" s="13">
         <v>20</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="10" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="C295" s="13">
         <v>20</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="10" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="C296" s="13">
         <v>20</v>
@@ -6965,10 +6965,10 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="10" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="C297" s="13">
         <v>20</v>
@@ -6982,10 +6982,10 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="10" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B298" s="10" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C298" s="13">
         <v>20</v>
@@ -6999,10 +6999,10 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="10" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="C299" s="13">
         <v>20</v>
@@ -7016,10 +7016,10 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="10" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="B300" s="10" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="C300" s="13">
         <v>20</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="10" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="B301" s="10" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="C301" s="13">
         <v>20</v>
@@ -7050,10 +7050,10 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="10" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="C302" s="13">
         <v>20</v>
@@ -7067,10 +7067,10 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="10" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C303" s="13">
         <v>20</v>
@@ -7084,10 +7084,10 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="10" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="C304" s="13">
         <v>20</v>
@@ -7101,10 +7101,10 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="10" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="C305" s="13">
         <v>20</v>
@@ -7118,10 +7118,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="10" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="C306" s="13">
         <v>20</v>
@@ -7135,10 +7135,10 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="10" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C307" s="13">
         <v>20</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="10" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="B308" s="10" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C308" s="13">
         <v>20</v>
@@ -7169,10 +7169,10 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="C309" s="13">
         <v>20</v>
@@ -7186,10 +7186,10 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="10" t="s">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="C310" s="13">
         <v>20</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C311" s="13">
         <v>20</v>
@@ -7220,10 +7220,10 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="10" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="C312" s="13">
         <v>20</v>
@@ -7237,10 +7237,10 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="10" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="C313" s="13">
         <v>20</v>
@@ -7254,10 +7254,10 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="10" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="C314" s="13">
         <v>20</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="10" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="C315" s="13">
         <v>20</v>
@@ -7288,10 +7288,10 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="10" t="s">
-        <v>223</v>
+        <v>145</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>223</v>
+        <v>145</v>
       </c>
       <c r="C316" s="13">
         <v>20</v>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="10" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="C317" s="13">
         <v>20</v>
@@ -7322,10 +7322,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="10" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C318" s="13">
         <v>20</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="10" t="s">
-        <v>228</v>
+        <v>147</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>228</v>
+        <v>147</v>
       </c>
       <c r="C319" s="13">
         <v>20</v>
@@ -7356,10 +7356,10 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="10" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C320" s="13">
         <v>20</v>
@@ -7373,27 +7373,27 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="10" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="C321" s="13">
         <v>20</v>
       </c>
       <c r="D321" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E321" s="11">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="E321" s="8">
+        <v>0.75</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="10" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>58</v>
+        <v>424</v>
       </c>
       <c r="C322" s="13">
         <v>20</v>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="10" t="s">
-        <v>40</v>
+        <v>363</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>424</v>
@@ -7424,7 +7424,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B324" s="10" t="s">
         <v>424</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="10" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B325" s="10" t="s">
         <v>424</v>
@@ -7458,10 +7458,10 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="10" t="s">
-        <v>379</v>
+        <v>77</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>424</v>
+        <v>77</v>
       </c>
       <c r="C326" s="13">
         <v>20</v>
@@ -7475,10 +7475,10 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="10" t="s">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="B327" s="10" t="s">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="C327" s="13">
         <v>20</v>
@@ -7492,10 +7492,10 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="10" t="s">
-        <v>386</v>
+        <v>72</v>
       </c>
       <c r="B328" s="10" t="s">
-        <v>386</v>
+        <v>72</v>
       </c>
       <c r="C328" s="13">
         <v>20</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="10" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B329" s="10" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C329" s="13">
         <v>20</v>
@@ -7526,10 +7526,10 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="10" t="s">
-        <v>61</v>
+        <v>382</v>
       </c>
       <c r="B330" s="10" t="s">
-        <v>61</v>
+        <v>382</v>
       </c>
       <c r="C330" s="13">
         <v>20</v>
@@ -7543,10 +7543,10 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="10" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B331" s="10" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C331" s="13">
         <v>20</v>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="10" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="B332" s="10" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="C332" s="13">
         <v>20</v>
@@ -7577,10 +7577,10 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="10" t="s">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="C333" s="13">
         <v>20</v>
@@ -7594,7 +7594,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="10" t="s">
-        <v>30</v>
+        <v>366</v>
       </c>
       <c r="B334" s="10" t="s">
         <v>425</v>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="10" t="s">
-        <v>366</v>
+        <v>52</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>425</v>
+        <v>52</v>
       </c>
       <c r="C335" s="13">
         <v>20</v>
@@ -7628,10 +7628,10 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="10" t="s">
-        <v>52</v>
+        <v>393</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>52</v>
+        <v>393</v>
       </c>
       <c r="C336" s="13">
         <v>20</v>
@@ -7645,10 +7645,10 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="10" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="B337" s="10" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="C337" s="13">
         <v>20</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="10" t="s">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="C338" s="13">
         <v>20</v>
@@ -7679,10 +7679,10 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="10" t="s">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="C339" s="13">
         <v>20</v>
@@ -7696,10 +7696,10 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="10" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="C340" s="13">
         <v>20</v>
@@ -7713,10 +7713,10 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="10" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C341" s="13">
         <v>20</v>
@@ -7730,10 +7730,10 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C342" s="13">
         <v>20</v>
@@ -7747,10 +7747,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C343" s="13">
         <v>20</v>
@@ -7764,10 +7764,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="10" t="s">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="C344" s="13">
         <v>20</v>
@@ -7781,10 +7781,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="10" t="s">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="C345" s="13">
         <v>20</v>
@@ -7798,10 +7798,10 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="10" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C346" s="13">
         <v>20</v>
@@ -7815,10 +7815,10 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="10" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C347" s="13">
         <v>20</v>
@@ -7832,10 +7832,10 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="10" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>392</v>
+        <v>431</v>
       </c>
       <c r="C348" s="13">
         <v>20</v>
@@ -7849,7 +7849,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="10" t="s">
-        <v>380</v>
+        <v>56</v>
       </c>
       <c r="B349" s="10" t="s">
         <v>431</v>
@@ -7866,10 +7866,10 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="10" t="s">
-        <v>56</v>
+        <v>394</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="C350" s="13">
         <v>20</v>
@@ -7883,10 +7883,10 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="10" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="B351" s="10" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="C351" s="13">
         <v>20</v>
@@ -7900,10 +7900,10 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="10" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="C352" s="13">
         <v>20</v>
@@ -7917,10 +7917,10 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="10" t="s">
-        <v>389</v>
+        <v>62</v>
       </c>
       <c r="B353" s="10" t="s">
-        <v>389</v>
+        <v>62</v>
       </c>
       <c r="C353" s="13">
         <v>20</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="10" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="B354" s="10" t="s">
-        <v>62</v>
+        <v>432</v>
       </c>
       <c r="C354" s="13">
         <v>20</v>
@@ -7951,7 +7951,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="10" t="s">
-        <v>35</v>
+        <v>373</v>
       </c>
       <c r="B355" s="10" t="s">
         <v>432</v>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B356" s="10" t="s">
         <v>432</v>
@@ -7985,7 +7985,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="10" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="B357" s="10" t="s">
         <v>432</v>
@@ -8002,10 +8002,10 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="10" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B358" s="10" t="s">
-        <v>432</v>
+        <v>391</v>
       </c>
       <c r="C358" s="13">
         <v>20</v>
@@ -8019,10 +8019,10 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="10" t="s">
-        <v>391</v>
+        <v>53</v>
       </c>
       <c r="B359" s="10" t="s">
-        <v>391</v>
+        <v>53</v>
       </c>
       <c r="C359" s="13">
         <v>20</v>
@@ -8036,10 +8036,10 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="10" t="s">
-        <v>53</v>
+        <v>375</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>53</v>
+        <v>375</v>
       </c>
       <c r="C360" s="13">
         <v>20</v>
@@ -8053,10 +8053,10 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="10" t="s">
-        <v>375</v>
+        <v>37</v>
       </c>
       <c r="B361" s="10" t="s">
-        <v>375</v>
+        <v>37</v>
       </c>
       <c r="C361" s="13">
         <v>20</v>
@@ -8070,13 +8070,13 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="10" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B362" s="10" t="s">
-        <v>37</v>
+        <v>426</v>
       </c>
       <c r="C362" s="13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D362" s="9" t="s">
         <v>24</v>
@@ -8087,7 +8087,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="10" t="s">
-        <v>23</v>
+        <v>376</v>
       </c>
       <c r="B363" s="10" t="s">
         <v>426</v>
@@ -8104,7 +8104,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B364" s="10" t="s">
         <v>426</v>
@@ -8121,7 +8121,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B365" s="10" t="s">
         <v>426</v>
@@ -8133,23 +8133,6 @@
         <v>24</v>
       </c>
       <c r="E365" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A366" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="B366" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C366" s="13">
-        <v>40</v>
-      </c>
-      <c r="D366" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E366" s="8">
         <v>0.75</v>
       </c>
     </row>

--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65230E5-B2C9-4699-B60E-AA07B6CAEC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9CDB3A-1B66-44C6-926E-FF885ADE0FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="435">
   <si>
     <t>Realizado_por</t>
   </si>
@@ -1338,6 +1338,9 @@
   </si>
   <si>
     <t>Nome_Consolidado</t>
+  </si>
+  <si>
+    <t>R-VALLE5</t>
   </si>
 </sst>
 </file>
@@ -1388,7 +1391,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1426,11 +1429,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1467,6 +1483,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1611,8 +1635,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E366" totalsRowShown="0">
-  <autoFilter ref="A1:E366" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E367" totalsRowShown="0">
+  <autoFilter ref="A1:E367" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="R-VALLE"/>
+        <filter val="R-VALLE2"/>
+        <filter val="R-VALLE3"/>
+        <filter val="R-VALLE4"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E366">
     <sortCondition ref="A1:A366"/>
   </sortState>
@@ -1924,7 +1957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD67F592-4C9C-4072-A458-8E5A8476F407}">
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E367"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="53.77734375" customWidth="1"/>
@@ -1950,7 +1983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>334</v>
       </c>
@@ -1967,7 +2000,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>67</v>
       </c>
@@ -1984,7 +2017,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>402</v>
       </c>
@@ -2001,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>399</v>
       </c>
@@ -2018,7 +2051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>401</v>
       </c>
@@ -2035,7 +2068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>335</v>
       </c>
@@ -2052,7 +2085,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>36</v>
       </c>
@@ -2069,7 +2102,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>336</v>
       </c>
@@ -2086,7 +2119,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>337</v>
       </c>
@@ -2103,7 +2136,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>384</v>
       </c>
@@ -2120,7 +2153,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>338</v>
       </c>
@@ -2137,7 +2170,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>339</v>
       </c>
@@ -2154,7 +2187,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>340</v>
       </c>
@@ -2171,7 +2204,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>341</v>
       </c>
@@ -2188,7 +2221,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>342</v>
       </c>
@@ -2205,7 +2238,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>343</v>
       </c>
@@ -2222,7 +2255,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>31</v>
       </c>
@@ -2239,7 +2272,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>344</v>
       </c>
@@ -2256,7 +2289,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>57</v>
       </c>
@@ -2273,7 +2306,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>388</v>
       </c>
@@ -2290,7 +2323,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>49</v>
       </c>
@@ -2307,7 +2340,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>68</v>
       </c>
@@ -2324,7 +2357,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>45</v>
       </c>
@@ -2341,7 +2374,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>345</v>
       </c>
@@ -2358,7 +2391,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>33</v>
       </c>
@@ -2375,7 +2408,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>346</v>
       </c>
@@ -2392,7 +2425,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>347</v>
       </c>
@@ -2409,7 +2442,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>71</v>
       </c>
@@ -2426,7 +2459,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>348</v>
       </c>
@@ -2443,7 +2476,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>134</v>
       </c>
@@ -2460,7 +2493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>93</v>
       </c>
@@ -2477,7 +2510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>88</v>
       </c>
@@ -2494,7 +2527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>316</v>
       </c>
@@ -2511,7 +2544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>100</v>
       </c>
@@ -2528,7 +2561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>99</v>
       </c>
@@ -2545,7 +2578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>105</v>
       </c>
@@ -2562,7 +2595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>98</v>
       </c>
@@ -2579,7 +2612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>84</v>
       </c>
@@ -2596,7 +2629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>92</v>
       </c>
@@ -2613,7 +2646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>89</v>
       </c>
@@ -2630,7 +2663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>317</v>
       </c>
@@ -2647,7 +2680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>106</v>
       </c>
@@ -2664,7 +2697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>112</v>
       </c>
@@ -2681,7 +2714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>94</v>
       </c>
@@ -2698,7 +2731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>318</v>
       </c>
@@ -2715,7 +2748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>90</v>
       </c>
@@ -2732,7 +2765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>108</v>
       </c>
@@ -2749,7 +2782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
@@ -2766,7 +2799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>319</v>
       </c>
@@ -2783,7 +2816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>109</v>
       </c>
@@ -2800,7 +2833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>96</v>
       </c>
@@ -2817,7 +2850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>85</v>
       </c>
@@ -2834,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>320</v>
       </c>
@@ -2851,7 +2884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>107</v>
       </c>
@@ -2868,7 +2901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>321</v>
       </c>
@@ -2885,7 +2918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>111</v>
       </c>
@@ -2902,7 +2935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>103</v>
       </c>
@@ -2919,7 +2952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>102</v>
       </c>
@@ -2936,7 +2969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>91</v>
       </c>
@@ -2953,7 +2986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>101</v>
       </c>
@@ -2970,7 +3003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>104</v>
       </c>
@@ -2987,7 +3020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>322</v>
       </c>
@@ -3004,7 +3037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>95</v>
       </c>
@@ -3021,7 +3054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>323</v>
       </c>
@@ -3038,7 +3071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>324</v>
       </c>
@@ -3055,7 +3088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>327</v>
       </c>
@@ -3072,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>86</v>
       </c>
@@ -3089,7 +3122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>110</v>
       </c>
@@ -3106,7 +3139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>325</v>
       </c>
@@ -3123,7 +3156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>97</v>
       </c>
@@ -3140,7 +3173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>257</v>
       </c>
@@ -3157,7 +3190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
         <v>301</v>
       </c>
@@ -3174,7 +3207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
         <v>302</v>
       </c>
@@ -3191,7 +3224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>253</v>
       </c>
@@ -3208,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>278</v>
       </c>
@@ -3225,7 +3258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
         <v>249</v>
       </c>
@@ -3242,7 +3275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
         <v>248</v>
       </c>
@@ -3259,7 +3292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
         <v>283</v>
       </c>
@@ -3276,7 +3309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
         <v>280</v>
       </c>
@@ -3293,7 +3326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="10" t="s">
         <v>303</v>
       </c>
@@ -3310,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>284</v>
       </c>
@@ -3327,7 +3360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
         <v>275</v>
       </c>
@@ -3344,7 +3377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>276</v>
       </c>
@@ -3361,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>304</v>
       </c>
@@ -3378,7 +3411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="10" t="s">
         <v>241</v>
       </c>
@@ -3395,7 +3428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="10" t="s">
         <v>279</v>
       </c>
@@ -3412,7 +3445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
         <v>397</v>
       </c>
@@ -3429,7 +3462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="10" t="s">
         <v>240</v>
       </c>
@@ -3446,7 +3479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
         <v>270</v>
       </c>
@@ -3463,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
         <v>263</v>
       </c>
@@ -3480,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
         <v>239</v>
       </c>
@@ -3497,7 +3530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
         <v>403</v>
       </c>
@@ -3512,7 +3545,7 @@
       </c>
       <c r="E93" s="8"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
         <v>252</v>
       </c>
@@ -3529,7 +3562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>247</v>
       </c>
@@ -3546,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
         <v>305</v>
       </c>
@@ -3563,7 +3596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="10" t="s">
         <v>244</v>
       </c>
@@ -3580,7 +3613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>274</v>
       </c>
@@ -3597,7 +3630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
         <v>161</v>
       </c>
@@ -3614,7 +3647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
         <v>306</v>
       </c>
@@ -3631,7 +3664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
         <v>242</v>
       </c>
@@ -3648,7 +3681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
         <v>243</v>
       </c>
@@ -3665,7 +3698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
         <v>231</v>
       </c>
@@ -3682,7 +3715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
         <v>265</v>
       </c>
@@ -3699,7 +3732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
         <v>282</v>
       </c>
@@ -3716,7 +3749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
         <v>236</v>
       </c>
@@ -3733,7 +3766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>254</v>
       </c>
@@ -3750,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
         <v>271</v>
       </c>
@@ -3767,7 +3800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
         <v>261</v>
       </c>
@@ -3784,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
         <v>255</v>
       </c>
@@ -3801,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
         <v>238</v>
       </c>
@@ -3818,7 +3851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
         <v>266</v>
       </c>
@@ -3835,7 +3868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
         <v>237</v>
       </c>
@@ -3852,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
         <v>113</v>
       </c>
@@ -3869,7 +3902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
         <v>233</v>
       </c>
@@ -3886,7 +3919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
         <v>404</v>
       </c>
@@ -3903,7 +3936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
         <v>229</v>
       </c>
@@ -3920,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="10" t="s">
         <v>286</v>
       </c>
@@ -3937,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="10" t="s">
         <v>277</v>
       </c>
@@ -3954,7 +3987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
         <v>256</v>
       </c>
@@ -3971,7 +4004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
         <v>246</v>
       </c>
@@ -3988,7 +4021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
         <v>333</v>
       </c>
@@ -4005,7 +4038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
         <v>187</v>
       </c>
@@ -4022,7 +4055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="10" t="s">
         <v>130</v>
       </c>
@@ -4039,7 +4072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="10" t="s">
         <v>264</v>
       </c>
@@ -4056,7 +4089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="10" t="s">
         <v>245</v>
       </c>
@@ -4073,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="10" t="s">
         <v>287</v>
       </c>
@@ -4090,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="10" t="s">
         <v>349</v>
       </c>
@@ -4107,7 +4140,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="10" t="s">
         <v>268</v>
       </c>
@@ -4124,7 +4157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="10" t="s">
         <v>285</v>
       </c>
@@ -4141,7 +4174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="10" t="s">
         <v>272</v>
       </c>
@@ -4158,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
         <v>250</v>
       </c>
@@ -4175,7 +4208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="10" t="s">
         <v>262</v>
       </c>
@@ -4192,7 +4225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="10" t="s">
         <v>232</v>
       </c>
@@ -4209,7 +4242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="10" t="s">
         <v>398</v>
       </c>
@@ -4226,7 +4259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="10" t="s">
         <v>259</v>
       </c>
@@ -4243,7 +4276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="10" t="s">
         <v>273</v>
       </c>
@@ -4260,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="10" t="s">
         <v>234</v>
       </c>
@@ -4277,7 +4310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="s">
         <v>235</v>
       </c>
@@ -4294,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="10" t="s">
         <v>281</v>
       </c>
@@ -4311,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="10" t="s">
         <v>269</v>
       </c>
@@ -4328,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="10" t="s">
         <v>267</v>
       </c>
@@ -4345,7 +4378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="10" t="s">
         <v>251</v>
       </c>
@@ -4362,7 +4395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="10" t="s">
         <v>258</v>
       </c>
@@ -4379,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="10" t="s">
         <v>260</v>
       </c>
@@ -4396,7 +4429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="10" t="s">
         <v>350</v>
       </c>
@@ -4413,7 +4446,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="10" t="s">
         <v>351</v>
       </c>
@@ -4430,7 +4463,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="10" t="s">
         <v>352</v>
       </c>
@@ -4447,7 +4480,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="10" t="s">
         <v>75</v>
       </c>
@@ -4464,7 +4497,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="10" t="s">
         <v>55</v>
       </c>
@@ -4481,7 +4514,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="10" t="s">
         <v>353</v>
       </c>
@@ -4498,7 +4531,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="10" t="s">
         <v>82</v>
       </c>
@@ -4515,7 +4548,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="10" t="s">
         <v>354</v>
       </c>
@@ -4532,7 +4565,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="10" t="s">
         <v>355</v>
       </c>
@@ -4549,7 +4582,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="10" t="s">
         <v>42</v>
       </c>
@@ -4566,7 +4599,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="10" t="s">
         <v>47</v>
       </c>
@@ -4583,7 +4616,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="10" t="s">
         <v>43</v>
       </c>
@@ -4600,7 +4633,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="10" t="s">
         <v>48</v>
       </c>
@@ -4617,7 +4650,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="10" t="s">
         <v>81</v>
       </c>
@@ -4634,7 +4667,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="10" t="s">
         <v>73</v>
       </c>
@@ -4651,7 +4684,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="10" t="s">
         <v>59</v>
       </c>
@@ -4668,7 +4701,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="10" t="s">
         <v>356</v>
       </c>
@@ -4685,7 +4718,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="10" t="s">
         <v>63</v>
       </c>
@@ -4702,7 +4735,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="10" t="s">
         <v>60</v>
       </c>
@@ -4719,7 +4752,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="10" t="s">
         <v>34</v>
       </c>
@@ -4736,7 +4769,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="10" t="s">
         <v>74</v>
       </c>
@@ -4753,7 +4786,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="10" t="s">
         <v>26</v>
       </c>
@@ -4770,7 +4803,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="10" t="s">
         <v>383</v>
       </c>
@@ -4787,7 +4820,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="10" t="s">
         <v>357</v>
       </c>
@@ -4804,7 +4837,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="10" t="s">
         <v>64</v>
       </c>
@@ -4821,7 +4854,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="10" t="s">
         <v>32</v>
       </c>
@@ -4838,7 +4871,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="10" t="s">
         <v>358</v>
       </c>
@@ -4855,7 +4888,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="10" t="s">
         <v>387</v>
       </c>
@@ -4872,7 +4905,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="10" t="s">
         <v>46</v>
       </c>
@@ -4889,7 +4922,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="10" t="s">
         <v>359</v>
       </c>
@@ -4906,7 +4939,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="10" t="s">
         <v>25</v>
       </c>
@@ -4923,7 +4956,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="10" t="s">
         <v>360</v>
       </c>
@@ -4940,7 +4973,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="10" t="s">
         <v>361</v>
       </c>
@@ -4957,7 +4990,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="10" t="s">
         <v>76</v>
       </c>
@@ -4974,7 +5007,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="10" t="s">
         <v>38</v>
       </c>
@@ -4991,7 +5024,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="10" t="s">
         <v>78</v>
       </c>
@@ -5008,7 +5041,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="10" t="s">
         <v>44</v>
       </c>
@@ -5025,7 +5058,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="10" t="s">
         <v>51</v>
       </c>
@@ -5042,7 +5075,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="10" t="s">
         <v>65</v>
       </c>
@@ -5059,7 +5092,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="10" t="s">
         <v>54</v>
       </c>
@@ -5076,7 +5109,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="10" t="s">
         <v>29</v>
       </c>
@@ -5093,7 +5126,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="10" t="s">
         <v>70</v>
       </c>
@@ -5110,7 +5143,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="10" t="s">
         <v>66</v>
       </c>
@@ -5127,7 +5160,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="10" t="s">
         <v>28</v>
       </c>
@@ -5144,7 +5177,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="10" t="s">
         <v>69</v>
       </c>
@@ -5161,7 +5194,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="10" t="s">
         <v>41</v>
       </c>
@@ -5178,7 +5211,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="10" t="s">
         <v>50</v>
       </c>
@@ -5195,7 +5228,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="10" t="s">
         <v>362</v>
       </c>
@@ -5212,7 +5245,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="10" t="s">
         <v>39</v>
       </c>
@@ -5229,7 +5262,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="10" t="s">
         <v>27</v>
       </c>
@@ -5246,7 +5279,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="10" t="s">
         <v>195</v>
       </c>
@@ -5263,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="10" t="s">
         <v>216</v>
       </c>
@@ -5280,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="10" t="s">
         <v>178</v>
       </c>
@@ -5297,7 +5330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="10" t="s">
         <v>121</v>
       </c>
@@ -5314,7 +5347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="10" t="s">
         <v>307</v>
       </c>
@@ -5331,7 +5364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="10" t="s">
         <v>116</v>
       </c>
@@ -5348,7 +5381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="10" t="s">
         <v>127</v>
       </c>
@@ -5365,7 +5398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="10" t="s">
         <v>119</v>
       </c>
@@ -5382,7 +5415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="10" t="s">
         <v>308</v>
       </c>
@@ -5399,7 +5432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="10" t="s">
         <v>115</v>
       </c>
@@ -5416,7 +5449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="10" t="s">
         <v>128</v>
       </c>
@@ -5433,7 +5466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="10" t="s">
         <v>131</v>
       </c>
@@ -5450,7 +5483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="10" t="s">
         <v>133</v>
       </c>
@@ -5467,7 +5500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="10" t="s">
         <v>309</v>
       </c>
@@ -5484,7 +5517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="10" t="s">
         <v>124</v>
       </c>
@@ -5501,7 +5534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="10" t="s">
         <v>310</v>
       </c>
@@ -5518,7 +5551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="10" t="s">
         <v>311</v>
       </c>
@@ -5535,7 +5568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="10" t="s">
         <v>125</v>
       </c>
@@ -5552,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="10" t="s">
         <v>129</v>
       </c>
@@ -5569,7 +5602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="10" t="s">
         <v>126</v>
       </c>
@@ -5586,7 +5619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="10" t="s">
         <v>312</v>
       </c>
@@ -5603,7 +5636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="10" t="s">
         <v>132</v>
       </c>
@@ -5620,7 +5653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="10" t="s">
         <v>117</v>
       </c>
@@ -5637,7 +5670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="10" t="s">
         <v>123</v>
       </c>
@@ -5654,7 +5687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="10" t="s">
         <v>313</v>
       </c>
@@ -5671,7 +5704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="10" t="s">
         <v>314</v>
       </c>
@@ -5688,7 +5721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="10" t="s">
         <v>120</v>
       </c>
@@ -5705,7 +5738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="10" t="s">
         <v>315</v>
       </c>
@@ -5722,7 +5755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="10" t="s">
         <v>118</v>
       </c>
@@ -5739,7 +5772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="10" t="s">
         <v>122</v>
       </c>
@@ -5756,7 +5789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="10" t="s">
         <v>183</v>
       </c>
@@ -5773,7 +5806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="10" t="s">
         <v>209</v>
       </c>
@@ -5790,7 +5823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="10" t="s">
         <v>139</v>
       </c>
@@ -5807,7 +5840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="10" t="s">
         <v>206</v>
       </c>
@@ -5824,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="10" t="s">
         <v>171</v>
       </c>
@@ -5841,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="10" t="s">
         <v>156</v>
       </c>
@@ -5858,7 +5891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="10" t="s">
         <v>143</v>
       </c>
@@ -5875,7 +5908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="10" t="s">
         <v>157</v>
       </c>
@@ -5892,7 +5925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="10" t="s">
         <v>173</v>
       </c>
@@ -5909,7 +5942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="10" t="s">
         <v>137</v>
       </c>
@@ -5926,7 +5959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="10" t="s">
         <v>179</v>
       </c>
@@ -5943,7 +5976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="10" t="s">
         <v>135</v>
       </c>
@@ -5960,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="10" t="s">
         <v>141</v>
       </c>
@@ -5977,7 +6010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="10" t="s">
         <v>215</v>
       </c>
@@ -5994,7 +6027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="10" t="s">
         <v>140</v>
       </c>
@@ -6011,7 +6044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="10" t="s">
         <v>166</v>
       </c>
@@ -6028,7 +6061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="10" t="s">
         <v>177</v>
       </c>
@@ -6045,7 +6078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="10" t="s">
         <v>172</v>
       </c>
@@ -6062,7 +6095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="15" t="s">
         <v>326</v>
       </c>
@@ -6079,7 +6112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="10" t="s">
         <v>288</v>
       </c>
@@ -6096,7 +6129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="10" t="s">
         <v>153</v>
       </c>
@@ -6113,7 +6146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="10" t="s">
         <v>164</v>
       </c>
@@ -6130,7 +6163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="10" t="s">
         <v>211</v>
       </c>
@@ -6147,7 +6180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="10" t="s">
         <v>226</v>
       </c>
@@ -6164,7 +6197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="10" t="s">
         <v>192</v>
       </c>
@@ -6181,7 +6214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="10" t="s">
         <v>151</v>
       </c>
@@ -6198,7 +6231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="10" t="s">
         <v>150</v>
       </c>
@@ -6215,7 +6248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="10" t="s">
         <v>199</v>
       </c>
@@ -6232,7 +6265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="10" t="s">
         <v>217</v>
       </c>
@@ -6249,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="10" t="s">
         <v>165</v>
       </c>
@@ -6266,7 +6299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="10" t="s">
         <v>201</v>
       </c>
@@ -6283,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="10" t="s">
         <v>224</v>
       </c>
@@ -6300,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="10" t="s">
         <v>194</v>
       </c>
@@ -6317,7 +6350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="10" t="s">
         <v>190</v>
       </c>
@@ -6334,7 +6367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="10" t="s">
         <v>197</v>
       </c>
@@ -6351,7 +6384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="10" t="s">
         <v>180</v>
       </c>
@@ -6368,7 +6401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="10" t="s">
         <v>212</v>
       </c>
@@ -6385,7 +6418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="10" t="s">
         <v>219</v>
       </c>
@@ -6402,7 +6435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="10" t="s">
         <v>198</v>
       </c>
@@ -6419,7 +6452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="10" t="s">
         <v>152</v>
       </c>
@@ -6436,7 +6469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="10" t="s">
         <v>189</v>
       </c>
@@ -6453,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="10" t="s">
         <v>155</v>
       </c>
@@ -6470,7 +6503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="10" t="s">
         <v>144</v>
       </c>
@@ -6487,7 +6520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="10" t="s">
         <v>162</v>
       </c>
@@ -6504,7 +6537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="10" t="s">
         <v>175</v>
       </c>
@@ -6521,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="10" t="s">
         <v>181</v>
       </c>
@@ -6538,7 +6571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="10" t="s">
         <v>188</v>
       </c>
@@ -6555,7 +6588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="10" t="s">
         <v>170</v>
       </c>
@@ -6572,7 +6605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="10" t="s">
         <v>221</v>
       </c>
@@ -6589,7 +6622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="10" t="s">
         <v>193</v>
       </c>
@@ -6606,7 +6639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="10" t="s">
         <v>208</v>
       </c>
@@ -6623,7 +6656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="10" t="s">
         <v>136</v>
       </c>
@@ -6640,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="10" t="s">
         <v>220</v>
       </c>
@@ -6657,7 +6690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="10" t="s">
         <v>186</v>
       </c>
@@ -6674,7 +6707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="10" t="s">
         <v>213</v>
       </c>
@@ -6691,7 +6724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="10" t="s">
         <v>149</v>
       </c>
@@ -6708,7 +6741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="10" t="s">
         <v>225</v>
       </c>
@@ -6725,7 +6758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="10" t="s">
         <v>182</v>
       </c>
@@ -6742,7 +6775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="10" t="s">
         <v>174</v>
       </c>
@@ -6759,7 +6792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="10" t="s">
         <v>138</v>
       </c>
@@ -6776,7 +6809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="10" t="s">
         <v>331</v>
       </c>
@@ -6793,7 +6826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="10" t="s">
         <v>332</v>
       </c>
@@ -6810,7 +6843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="10" t="s">
         <v>329</v>
       </c>
@@ -6827,7 +6860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="10" t="s">
         <v>330</v>
       </c>
@@ -6844,7 +6877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="10" t="s">
         <v>185</v>
       </c>
@@ -6861,7 +6894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="10" t="s">
         <v>203</v>
       </c>
@@ -6878,7 +6911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="10" t="s">
         <v>200</v>
       </c>
@@ -6895,7 +6928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="10" t="s">
         <v>204</v>
       </c>
@@ -6912,7 +6945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="10" t="s">
         <v>163</v>
       </c>
@@ -6929,7 +6962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="10" t="s">
         <v>146</v>
       </c>
@@ -6946,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="10" t="s">
         <v>202</v>
       </c>
@@ -6963,7 +6996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="10" t="s">
         <v>169</v>
       </c>
@@ -6980,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="10" t="s">
         <v>160</v>
       </c>
@@ -6997,7 +7030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="10" t="s">
         <v>218</v>
       </c>
@@ -7014,7 +7047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="10" t="s">
         <v>158</v>
       </c>
@@ -7031,7 +7064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="10" t="s">
         <v>207</v>
       </c>
@@ -7048,7 +7081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="10" t="s">
         <v>184</v>
       </c>
@@ -7065,7 +7098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="10" t="s">
         <v>168</v>
       </c>
@@ -7082,7 +7115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="10" t="s">
         <v>196</v>
       </c>
@@ -7099,7 +7132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="10" t="s">
         <v>210</v>
       </c>
@@ -7116,7 +7149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="10" t="s">
         <v>159</v>
       </c>
@@ -7133,7 +7166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="10" t="s">
         <v>167</v>
       </c>
@@ -7150,7 +7183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="10" t="s">
         <v>191</v>
       </c>
@@ -7167,7 +7200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
         <v>154</v>
       </c>
@@ -7184,7 +7217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="10" t="s">
         <v>227</v>
       </c>
@@ -7201,7 +7234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
         <v>222</v>
       </c>
@@ -7218,7 +7251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="10" t="s">
         <v>205</v>
       </c>
@@ -7235,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="10" t="s">
         <v>176</v>
       </c>
@@ -7252,7 +7285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="10" t="s">
         <v>148</v>
       </c>
@@ -7269,7 +7302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="10" t="s">
         <v>223</v>
       </c>
@@ -7286,7 +7319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="10" t="s">
         <v>145</v>
       </c>
@@ -7303,7 +7336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="10" t="s">
         <v>214</v>
       </c>
@@ -7320,7 +7353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="10" t="s">
         <v>228</v>
       </c>
@@ -7337,7 +7370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="10" t="s">
         <v>147</v>
       </c>
@@ -7354,7 +7387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="10" t="s">
         <v>142</v>
       </c>
@@ -7371,7 +7404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="10" t="s">
         <v>58</v>
       </c>
@@ -7388,7 +7421,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="10" t="s">
         <v>40</v>
       </c>
@@ -7405,7 +7438,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="10" t="s">
         <v>363</v>
       </c>
@@ -7422,7 +7455,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="10" t="s">
         <v>364</v>
       </c>
@@ -7439,7 +7472,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="10" t="s">
         <v>379</v>
       </c>
@@ -7456,7 +7489,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="10" t="s">
         <v>77</v>
       </c>
@@ -7473,7 +7506,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="10" t="s">
         <v>386</v>
       </c>
@@ -7490,7 +7523,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="10" t="s">
         <v>72</v>
       </c>
@@ -7507,7 +7540,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="10" t="s">
         <v>61</v>
       </c>
@@ -7524,7 +7557,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="10" t="s">
         <v>382</v>
       </c>
@@ -7541,7 +7574,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="10" t="s">
         <v>385</v>
       </c>
@@ -7558,7 +7591,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="10" t="s">
         <v>365</v>
       </c>
@@ -7575,7 +7608,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="10" t="s">
         <v>30</v>
       </c>
@@ -7592,7 +7625,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="10" t="s">
         <v>366</v>
       </c>
@@ -7609,7 +7642,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="10" t="s">
         <v>52</v>
       </c>
@@ -7626,7 +7659,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="10" t="s">
         <v>393</v>
       </c>
@@ -7643,7 +7676,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="10" t="s">
         <v>367</v>
       </c>
@@ -7660,7 +7693,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="10" t="s">
         <v>80</v>
       </c>
@@ -7677,7 +7710,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="10" t="s">
         <v>368</v>
       </c>
@@ -7694,7 +7727,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="10" t="s">
         <v>381</v>
       </c>
@@ -7711,7 +7744,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="10" t="s">
         <v>369</v>
       </c>
@@ -7728,7 +7761,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="10" t="s">
         <v>370</v>
       </c>
@@ -7745,7 +7778,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="10" t="s">
         <v>371</v>
       </c>
@@ -7762,7 +7795,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="10" t="s">
         <v>79</v>
       </c>
@@ -7779,7 +7812,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="10" t="s">
         <v>390</v>
       </c>
@@ -7796,7 +7829,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="10" t="s">
         <v>396</v>
       </c>
@@ -7813,7 +7846,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="10" t="s">
         <v>392</v>
       </c>
@@ -7830,7 +7863,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="10" t="s">
         <v>380</v>
       </c>
@@ -7847,7 +7880,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="10" t="s">
         <v>56</v>
       </c>
@@ -7864,7 +7897,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="10" t="s">
         <v>394</v>
       </c>
@@ -7881,7 +7914,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="10" t="s">
         <v>372</v>
       </c>
@@ -7898,7 +7931,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="10" t="s">
         <v>389</v>
       </c>
@@ -7915,7 +7948,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="10" t="s">
         <v>62</v>
       </c>
@@ -8000,7 +8033,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="10" t="s">
         <v>391</v>
       </c>
@@ -8017,7 +8050,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="10" t="s">
         <v>53</v>
       </c>
@@ -8034,7 +8067,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="10" t="s">
         <v>375</v>
       </c>
@@ -8051,7 +8084,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="10" t="s">
         <v>37</v>
       </c>
@@ -8068,7 +8101,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="10" t="s">
         <v>23</v>
       </c>
@@ -8085,7 +8118,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="10" t="s">
         <v>376</v>
       </c>
@@ -8102,7 +8135,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="10" t="s">
         <v>377</v>
       </c>
@@ -8119,7 +8152,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="10" t="s">
         <v>378</v>
       </c>
@@ -8133,6 +8166,24 @@
         <v>24</v>
       </c>
       <c r="E365" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A367" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B367" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="C367" s="17">
+        <v>20</v>
+      </c>
+      <c r="D367" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E367" s="19">
         <v>0.75</v>
       </c>
     </row>

--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9CDB3A-1B66-44C6-926E-FF885ADE0FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639F60EB-DE92-4892-B848-8D4C19268550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
@@ -1639,10 +1639,15 @@
   <autoFilter ref="A1:E367" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}">
     <filterColumn colId="0">
       <filters>
-        <filter val="R-VALLE"/>
-        <filter val="R-VALLE2"/>
-        <filter val="R-VALLE3"/>
-        <filter val="R-VALLE4"/>
+        <filter val="EG-APAZA1"/>
+        <filter val="EG-APAZA2"/>
+        <filter val="EG-APAZA3"/>
+        <filter val="EG-APAZA4"/>
+        <filter val="EG-APAZA5"/>
+        <filter val="EG-APAZA6"/>
+        <filter val="EG-APAZA7"/>
+        <filter val="EG-APAZA8"/>
+        <filter val="EG-APAZA9"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2085,7 +2090,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>36</v>
       </c>
@@ -2093,7 +2098,7 @@
         <v>416</v>
       </c>
       <c r="C8" s="13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>24</v>
@@ -2102,7 +2107,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>336</v>
       </c>
@@ -2119,7 +2124,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>337</v>
       </c>
@@ -2136,7 +2141,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>384</v>
       </c>
@@ -2153,7 +2158,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>338</v>
       </c>
@@ -2170,7 +2175,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>339</v>
       </c>
@@ -2187,7 +2192,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>340</v>
       </c>
@@ -2204,7 +2209,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>341</v>
       </c>
@@ -2221,7 +2226,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>342</v>
       </c>
@@ -7965,7 +7970,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="10" t="s">
         <v>35</v>
       </c>
@@ -7982,7 +7987,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="10" t="s">
         <v>373</v>
       </c>
@@ -7999,7 +8004,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="10" t="s">
         <v>374</v>
       </c>
@@ -8016,7 +8021,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="10" t="s">
         <v>395</v>
       </c>
@@ -8170,7 +8175,7 @@
       </c>
     </row>
     <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="16" t="s">
         <v>434</v>
       </c>

--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639F60EB-DE92-4892-B848-8D4C19268550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BFE381-CC10-44E9-891D-7E1894958B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="458">
   <si>
     <t>Realizado_por</t>
   </si>
@@ -1341,13 +1341,82 @@
   </si>
   <si>
     <t>R-VALLE5</t>
+  </si>
+  <si>
+    <t>HHA-CAME</t>
+  </si>
+  <si>
+    <t>HHA-DJEAN</t>
+  </si>
+  <si>
+    <t>HHA-GEMY</t>
+  </si>
+  <si>
+    <t>HHA-ZILUS</t>
+  </si>
+  <si>
+    <t>HHF-WALNES</t>
+  </si>
+  <si>
+    <t>HHJ-FABIEN</t>
+  </si>
+  <si>
+    <t>HHR-JOSEPH</t>
+  </si>
+  <si>
+    <t>HHR-KETEL</t>
+  </si>
+  <si>
+    <t>HHW-BERMAN</t>
+  </si>
+  <si>
+    <t>HHW-JAMES</t>
+  </si>
+  <si>
+    <t>HMA-LUKEN</t>
+  </si>
+  <si>
+    <t>HRO-LOUIS</t>
+  </si>
+  <si>
+    <t>HSO-CHENEL</t>
+  </si>
+  <si>
+    <t>MB-ANDREA</t>
+  </si>
+  <si>
+    <t>MB-CHEDELY</t>
+  </si>
+  <si>
+    <t>MB-FERRY</t>
+  </si>
+  <si>
+    <t>MB-FREDNER</t>
+  </si>
+  <si>
+    <t>MB-JACQUES</t>
+  </si>
+  <si>
+    <t>MB-VANESS1</t>
+  </si>
+  <si>
+    <t>MB-WELSON</t>
+  </si>
+  <si>
+    <t>R-COLQUE</t>
+  </si>
+  <si>
+    <t>R-DAVID</t>
+  </si>
+  <si>
+    <t>SONEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1382,13 +1451,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -1446,7 +1527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1491,6 +1572,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1635,24 +1722,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E367" totalsRowShown="0">
-  <autoFilter ref="A1:E367" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="EG-APAZA1"/>
-        <filter val="EG-APAZA2"/>
-        <filter val="EG-APAZA3"/>
-        <filter val="EG-APAZA4"/>
-        <filter val="EG-APAZA5"/>
-        <filter val="EG-APAZA6"/>
-        <filter val="EG-APAZA7"/>
-        <filter val="EG-APAZA8"/>
-        <filter val="EG-APAZA9"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E366">
-    <sortCondition ref="A1:A366"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E389" totalsRowShown="0">
+  <autoFilter ref="A1:E389" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E365">
+    <sortCondition ref="A1:A365"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A4BD7FC1-F519-41FB-AA5E-E1B407B65298}" name="Realizado_por" dataDxfId="4"/>
@@ -1962,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD67F592-4C9C-4072-A458-8E5A8476F407}">
-  <dimension ref="A1:E367"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="53.77734375" customWidth="1"/>
@@ -1988,7 +2061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>334</v>
       </c>
@@ -2005,7 +2078,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>67</v>
       </c>
@@ -2022,7 +2095,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>402</v>
       </c>
@@ -2039,7 +2112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>399</v>
       </c>
@@ -2056,7 +2129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>401</v>
       </c>
@@ -2073,7 +2146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>335</v>
       </c>
@@ -2243,7 +2316,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>343</v>
       </c>
@@ -2260,7 +2333,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>31</v>
       </c>
@@ -2277,7 +2350,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>344</v>
       </c>
@@ -2294,7 +2367,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>57</v>
       </c>
@@ -2311,7 +2384,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>388</v>
       </c>
@@ -2328,7 +2401,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>49</v>
       </c>
@@ -2345,7 +2418,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>68</v>
       </c>
@@ -2362,7 +2435,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>45</v>
       </c>
@@ -2379,7 +2452,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>345</v>
       </c>
@@ -2396,7 +2469,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>33</v>
       </c>
@@ -2413,7 +2486,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>346</v>
       </c>
@@ -2430,7 +2503,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>347</v>
       </c>
@@ -2447,7 +2520,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>71</v>
       </c>
@@ -2464,7 +2537,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>348</v>
       </c>
@@ -2481,7 +2554,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>134</v>
       </c>
@@ -2498,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>93</v>
       </c>
@@ -2515,7 +2588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>88</v>
       </c>
@@ -2532,7 +2605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>316</v>
       </c>
@@ -2549,7 +2622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>100</v>
       </c>
@@ -2566,7 +2639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>99</v>
       </c>
@@ -2583,7 +2656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>105</v>
       </c>
@@ -2600,7 +2673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>98</v>
       </c>
@@ -2617,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>84</v>
       </c>
@@ -2634,7 +2707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>92</v>
       </c>
@@ -2651,7 +2724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>89</v>
       </c>
@@ -2668,7 +2741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>317</v>
       </c>
@@ -2685,7 +2758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>106</v>
       </c>
@@ -2702,7 +2775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>112</v>
       </c>
@@ -2719,7 +2792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>94</v>
       </c>
@@ -2736,7 +2809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>318</v>
       </c>
@@ -2753,7 +2826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>90</v>
       </c>
@@ -2770,7 +2843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>108</v>
       </c>
@@ -2787,7 +2860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
@@ -2804,7 +2877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>319</v>
       </c>
@@ -2821,7 +2894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>109</v>
       </c>
@@ -2838,7 +2911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>96</v>
       </c>
@@ -2855,7 +2928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>85</v>
       </c>
@@ -2872,7 +2945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>320</v>
       </c>
@@ -2889,7 +2962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>107</v>
       </c>
@@ -2906,7 +2979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>321</v>
       </c>
@@ -2923,7 +2996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>111</v>
       </c>
@@ -2940,7 +3013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>103</v>
       </c>
@@ -2957,7 +3030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>102</v>
       </c>
@@ -2974,7 +3047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>91</v>
       </c>
@@ -2991,7 +3064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>101</v>
       </c>
@@ -3008,7 +3081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>104</v>
       </c>
@@ -3025,7 +3098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>322</v>
       </c>
@@ -3042,7 +3115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>95</v>
       </c>
@@ -3059,7 +3132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>323</v>
       </c>
@@ -3076,7 +3149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>324</v>
       </c>
@@ -3093,7 +3166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>327</v>
       </c>
@@ -3110,7 +3183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>86</v>
       </c>
@@ -3127,7 +3200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>110</v>
       </c>
@@ -3144,7 +3217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>325</v>
       </c>
@@ -3161,7 +3234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>97</v>
       </c>
@@ -3178,7 +3251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>257</v>
       </c>
@@ -3195,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
         <v>301</v>
       </c>
@@ -3212,7 +3285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
         <v>302</v>
       </c>
@@ -3229,7 +3302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>253</v>
       </c>
@@ -3246,7 +3319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>278</v>
       </c>
@@ -3263,7 +3336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
         <v>249</v>
       </c>
@@ -3280,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
         <v>248</v>
       </c>
@@ -3297,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
         <v>283</v>
       </c>
@@ -3314,7 +3387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
         <v>280</v>
       </c>
@@ -3331,7 +3404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="10" t="s">
         <v>303</v>
       </c>
@@ -3348,7 +3421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>284</v>
       </c>
@@ -3365,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
         <v>275</v>
       </c>
@@ -3382,7 +3455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>276</v>
       </c>
@@ -3399,7 +3472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>304</v>
       </c>
@@ -3416,7 +3489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="10" t="s">
         <v>241</v>
       </c>
@@ -3433,7 +3506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="10" t="s">
         <v>279</v>
       </c>
@@ -3450,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
         <v>397</v>
       </c>
@@ -3467,7 +3540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="10" t="s">
         <v>240</v>
       </c>
@@ -3484,7 +3557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
         <v>270</v>
       </c>
@@ -3501,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
         <v>263</v>
       </c>
@@ -3518,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
         <v>239</v>
       </c>
@@ -3535,7 +3608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
         <v>403</v>
       </c>
@@ -3550,7 +3623,7 @@
       </c>
       <c r="E93" s="8"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
         <v>252</v>
       </c>
@@ -3567,7 +3640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>247</v>
       </c>
@@ -3584,7 +3657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
         <v>305</v>
       </c>
@@ -3601,7 +3674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="10" t="s">
         <v>244</v>
       </c>
@@ -3618,7 +3691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>274</v>
       </c>
@@ -3635,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
         <v>161</v>
       </c>
@@ -3652,7 +3725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
         <v>306</v>
       </c>
@@ -3669,7 +3742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
         <v>242</v>
       </c>
@@ -3686,7 +3759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
         <v>243</v>
       </c>
@@ -3703,7 +3776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
         <v>231</v>
       </c>
@@ -3720,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
         <v>265</v>
       </c>
@@ -3737,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
         <v>282</v>
       </c>
@@ -3754,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
         <v>236</v>
       </c>
@@ -3771,7 +3844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>254</v>
       </c>
@@ -3788,7 +3861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
         <v>271</v>
       </c>
@@ -3805,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
         <v>261</v>
       </c>
@@ -3822,7 +3895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
         <v>255</v>
       </c>
@@ -3839,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
         <v>238</v>
       </c>
@@ -3856,7 +3929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
         <v>266</v>
       </c>
@@ -3873,7 +3946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
         <v>237</v>
       </c>
@@ -3890,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
         <v>113</v>
       </c>
@@ -3907,7 +3980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
         <v>233</v>
       </c>
@@ -3924,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
         <v>404</v>
       </c>
@@ -3941,7 +4014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
         <v>229</v>
       </c>
@@ -3958,7 +4031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="10" t="s">
         <v>286</v>
       </c>
@@ -3975,7 +4048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="10" t="s">
         <v>277</v>
       </c>
@@ -3992,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
         <v>256</v>
       </c>
@@ -4009,7 +4082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
         <v>246</v>
       </c>
@@ -4026,7 +4099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
         <v>333</v>
       </c>
@@ -4043,7 +4116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
         <v>187</v>
       </c>
@@ -4060,7 +4133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="10" t="s">
         <v>130</v>
       </c>
@@ -4077,7 +4150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="10" t="s">
         <v>264</v>
       </c>
@@ -4094,7 +4167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="10" t="s">
         <v>245</v>
       </c>
@@ -4111,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="10" t="s">
         <v>287</v>
       </c>
@@ -4128,7 +4201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="10" t="s">
         <v>349</v>
       </c>
@@ -4145,7 +4218,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="10" t="s">
         <v>268</v>
       </c>
@@ -4162,7 +4235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="10" t="s">
         <v>285</v>
       </c>
@@ -4179,7 +4252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="10" t="s">
         <v>272</v>
       </c>
@@ -4196,7 +4269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
         <v>250</v>
       </c>
@@ -4213,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="10" t="s">
         <v>262</v>
       </c>
@@ -4230,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="10" t="s">
         <v>232</v>
       </c>
@@ -4247,7 +4320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="10" t="s">
         <v>398</v>
       </c>
@@ -4264,7 +4337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="10" t="s">
         <v>259</v>
       </c>
@@ -4281,7 +4354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="10" t="s">
         <v>273</v>
       </c>
@@ -4298,7 +4371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="10" t="s">
         <v>234</v>
       </c>
@@ -4315,7 +4388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="s">
         <v>235</v>
       </c>
@@ -4332,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="10" t="s">
         <v>281</v>
       </c>
@@ -4349,7 +4422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="10" t="s">
         <v>269</v>
       </c>
@@ -4366,7 +4439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="10" t="s">
         <v>267</v>
       </c>
@@ -4383,7 +4456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="10" t="s">
         <v>251</v>
       </c>
@@ -4400,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="10" t="s">
         <v>258</v>
       </c>
@@ -4417,7 +4490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="10" t="s">
         <v>260</v>
       </c>
@@ -4434,7 +4507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="10" t="s">
         <v>350</v>
       </c>
@@ -4451,7 +4524,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="10" t="s">
         <v>351</v>
       </c>
@@ -4468,7 +4541,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="10" t="s">
         <v>352</v>
       </c>
@@ -4485,7 +4558,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="10" t="s">
         <v>75</v>
       </c>
@@ -4502,7 +4575,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="10" t="s">
         <v>55</v>
       </c>
@@ -4519,7 +4592,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="10" t="s">
         <v>353</v>
       </c>
@@ -4536,7 +4609,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="10" t="s">
         <v>82</v>
       </c>
@@ -4553,7 +4626,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="10" t="s">
         <v>354</v>
       </c>
@@ -4570,7 +4643,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="10" t="s">
         <v>355</v>
       </c>
@@ -4587,7 +4660,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="10" t="s">
         <v>42</v>
       </c>
@@ -4604,7 +4677,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="10" t="s">
         <v>47</v>
       </c>
@@ -4621,7 +4694,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="10" t="s">
         <v>43</v>
       </c>
@@ -4638,7 +4711,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="10" t="s">
         <v>48</v>
       </c>
@@ -4655,7 +4728,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="10" t="s">
         <v>81</v>
       </c>
@@ -4672,7 +4745,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="10" t="s">
         <v>73</v>
       </c>
@@ -4689,7 +4762,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="10" t="s">
         <v>59</v>
       </c>
@@ -4706,7 +4779,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="10" t="s">
         <v>356</v>
       </c>
@@ -4723,7 +4796,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="10" t="s">
         <v>63</v>
       </c>
@@ -4740,7 +4813,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="10" t="s">
         <v>60</v>
       </c>
@@ -4757,7 +4830,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="10" t="s">
         <v>34</v>
       </c>
@@ -4774,7 +4847,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="10" t="s">
         <v>74</v>
       </c>
@@ -4791,7 +4864,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="10" t="s">
         <v>26</v>
       </c>
@@ -4808,7 +4881,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="10" t="s">
         <v>383</v>
       </c>
@@ -4825,7 +4898,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="10" t="s">
         <v>357</v>
       </c>
@@ -4842,7 +4915,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="10" t="s">
         <v>64</v>
       </c>
@@ -4859,7 +4932,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="10" t="s">
         <v>32</v>
       </c>
@@ -4876,7 +4949,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="10" t="s">
         <v>358</v>
       </c>
@@ -4893,7 +4966,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="10" t="s">
         <v>387</v>
       </c>
@@ -4910,7 +4983,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="10" t="s">
         <v>46</v>
       </c>
@@ -4927,7 +5000,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="10" t="s">
         <v>359</v>
       </c>
@@ -4944,7 +5017,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="10" t="s">
         <v>25</v>
       </c>
@@ -4961,7 +5034,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="10" t="s">
         <v>360</v>
       </c>
@@ -4978,7 +5051,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="10" t="s">
         <v>361</v>
       </c>
@@ -4995,7 +5068,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="10" t="s">
         <v>76</v>
       </c>
@@ -5012,7 +5085,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="10" t="s">
         <v>38</v>
       </c>
@@ -5029,7 +5102,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="10" t="s">
         <v>78</v>
       </c>
@@ -5046,7 +5119,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="10" t="s">
         <v>44</v>
       </c>
@@ -5063,7 +5136,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="10" t="s">
         <v>51</v>
       </c>
@@ -5080,7 +5153,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="10" t="s">
         <v>65</v>
       </c>
@@ -5097,7 +5170,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="10" t="s">
         <v>54</v>
       </c>
@@ -5114,7 +5187,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="10" t="s">
         <v>29</v>
       </c>
@@ -5131,7 +5204,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="10" t="s">
         <v>70</v>
       </c>
@@ -5148,7 +5221,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="10" t="s">
         <v>66</v>
       </c>
@@ -5165,7 +5238,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="10" t="s">
         <v>28</v>
       </c>
@@ -5182,7 +5255,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="10" t="s">
         <v>69</v>
       </c>
@@ -5199,7 +5272,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="10" t="s">
         <v>41</v>
       </c>
@@ -5216,7 +5289,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="10" t="s">
         <v>50</v>
       </c>
@@ -5233,7 +5306,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="10" t="s">
         <v>362</v>
       </c>
@@ -5250,7 +5323,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="10" t="s">
         <v>39</v>
       </c>
@@ -5267,7 +5340,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="10" t="s">
         <v>27</v>
       </c>
@@ -5284,7 +5357,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="10" t="s">
         <v>195</v>
       </c>
@@ -5301,7 +5374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="10" t="s">
         <v>216</v>
       </c>
@@ -5318,7 +5391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="10" t="s">
         <v>178</v>
       </c>
@@ -5335,7 +5408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="10" t="s">
         <v>121</v>
       </c>
@@ -5352,7 +5425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="10" t="s">
         <v>307</v>
       </c>
@@ -5369,7 +5442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="10" t="s">
         <v>116</v>
       </c>
@@ -5386,7 +5459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="10" t="s">
         <v>127</v>
       </c>
@@ -5403,7 +5476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="10" t="s">
         <v>119</v>
       </c>
@@ -5420,7 +5493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="10" t="s">
         <v>308</v>
       </c>
@@ -5437,7 +5510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="10" t="s">
         <v>115</v>
       </c>
@@ -5454,7 +5527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="10" t="s">
         <v>128</v>
       </c>
@@ -5471,7 +5544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="10" t="s">
         <v>131</v>
       </c>
@@ -5488,7 +5561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="10" t="s">
         <v>133</v>
       </c>
@@ -5505,7 +5578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="10" t="s">
         <v>309</v>
       </c>
@@ -5522,7 +5595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="10" t="s">
         <v>124</v>
       </c>
@@ -5539,7 +5612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="10" t="s">
         <v>310</v>
       </c>
@@ -5556,7 +5629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="10" t="s">
         <v>311</v>
       </c>
@@ -5573,7 +5646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="10" t="s">
         <v>125</v>
       </c>
@@ -5590,7 +5663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="10" t="s">
         <v>129</v>
       </c>
@@ -5607,7 +5680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="10" t="s">
         <v>126</v>
       </c>
@@ -5624,7 +5697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="10" t="s">
         <v>312</v>
       </c>
@@ -5641,7 +5714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="10" t="s">
         <v>132</v>
       </c>
@@ -5658,7 +5731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="10" t="s">
         <v>117</v>
       </c>
@@ -5675,7 +5748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="10" t="s">
         <v>123</v>
       </c>
@@ -5692,7 +5765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="10" t="s">
         <v>313</v>
       </c>
@@ -5709,7 +5782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="10" t="s">
         <v>314</v>
       </c>
@@ -5726,7 +5799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="10" t="s">
         <v>120</v>
       </c>
@@ -5743,7 +5816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="10" t="s">
         <v>315</v>
       </c>
@@ -5760,7 +5833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="10" t="s">
         <v>118</v>
       </c>
@@ -5777,7 +5850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="10" t="s">
         <v>122</v>
       </c>
@@ -5794,7 +5867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="10" t="s">
         <v>183</v>
       </c>
@@ -5811,7 +5884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="10" t="s">
         <v>209</v>
       </c>
@@ -5828,7 +5901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="10" t="s">
         <v>139</v>
       </c>
@@ -5845,7 +5918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="10" t="s">
         <v>206</v>
       </c>
@@ -5862,7 +5935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="10" t="s">
         <v>171</v>
       </c>
@@ -5879,7 +5952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="10" t="s">
         <v>156</v>
       </c>
@@ -5896,7 +5969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="10" t="s">
         <v>143</v>
       </c>
@@ -5913,7 +5986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="10" t="s">
         <v>157</v>
       </c>
@@ -5930,7 +6003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="10" t="s">
         <v>173</v>
       </c>
@@ -5947,7 +6020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="10" t="s">
         <v>137</v>
       </c>
@@ -5964,7 +6037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="10" t="s">
         <v>179</v>
       </c>
@@ -5981,7 +6054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="10" t="s">
         <v>135</v>
       </c>
@@ -5998,7 +6071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="10" t="s">
         <v>141</v>
       </c>
@@ -6015,7 +6088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="10" t="s">
         <v>215</v>
       </c>
@@ -6032,7 +6105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="10" t="s">
         <v>140</v>
       </c>
@@ -6049,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="10" t="s">
         <v>166</v>
       </c>
@@ -6066,7 +6139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="10" t="s">
         <v>177</v>
       </c>
@@ -6083,7 +6156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="10" t="s">
         <v>172</v>
       </c>
@@ -6100,7 +6173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="15" t="s">
         <v>326</v>
       </c>
@@ -6117,7 +6190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="10" t="s">
         <v>288</v>
       </c>
@@ -6134,7 +6207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="10" t="s">
         <v>153</v>
       </c>
@@ -6151,7 +6224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="10" t="s">
         <v>164</v>
       </c>
@@ -6168,7 +6241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="10" t="s">
         <v>211</v>
       </c>
@@ -6185,7 +6258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="10" t="s">
         <v>226</v>
       </c>
@@ -6202,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="10" t="s">
         <v>192</v>
       </c>
@@ -6219,7 +6292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="10" t="s">
         <v>151</v>
       </c>
@@ -6236,7 +6309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="10" t="s">
         <v>150</v>
       </c>
@@ -6253,7 +6326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="10" t="s">
         <v>199</v>
       </c>
@@ -6270,7 +6343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="10" t="s">
         <v>217</v>
       </c>
@@ -6287,7 +6360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="10" t="s">
         <v>165</v>
       </c>
@@ -6304,7 +6377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="10" t="s">
         <v>201</v>
       </c>
@@ -6321,7 +6394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="10" t="s">
         <v>224</v>
       </c>
@@ -6338,7 +6411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="10" t="s">
         <v>194</v>
       </c>
@@ -6355,7 +6428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="10" t="s">
         <v>190</v>
       </c>
@@ -6372,7 +6445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="10" t="s">
         <v>197</v>
       </c>
@@ -6389,7 +6462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="10" t="s">
         <v>180</v>
       </c>
@@ -6406,7 +6479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="10" t="s">
         <v>212</v>
       </c>
@@ -6423,7 +6496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="10" t="s">
         <v>219</v>
       </c>
@@ -6440,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="10" t="s">
         <v>198</v>
       </c>
@@ -6457,7 +6530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="10" t="s">
         <v>152</v>
       </c>
@@ -6474,7 +6547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="10" t="s">
         <v>189</v>
       </c>
@@ -6491,7 +6564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="10" t="s">
         <v>155</v>
       </c>
@@ -6508,7 +6581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="10" t="s">
         <v>144</v>
       </c>
@@ -6525,7 +6598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="10" t="s">
         <v>162</v>
       </c>
@@ -6542,7 +6615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="10" t="s">
         <v>175</v>
       </c>
@@ -6559,7 +6632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="10" t="s">
         <v>181</v>
       </c>
@@ -6576,7 +6649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="10" t="s">
         <v>188</v>
       </c>
@@ -6593,7 +6666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="10" t="s">
         <v>170</v>
       </c>
@@ -6610,7 +6683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="10" t="s">
         <v>221</v>
       </c>
@@ -6627,7 +6700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="10" t="s">
         <v>193</v>
       </c>
@@ -6644,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="10" t="s">
         <v>208</v>
       </c>
@@ -6661,7 +6734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="10" t="s">
         <v>136</v>
       </c>
@@ -6678,7 +6751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="10" t="s">
         <v>220</v>
       </c>
@@ -6695,7 +6768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="10" t="s">
         <v>186</v>
       </c>
@@ -6712,7 +6785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="10" t="s">
         <v>213</v>
       </c>
@@ -6729,7 +6802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="10" t="s">
         <v>149</v>
       </c>
@@ -6746,7 +6819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="10" t="s">
         <v>225</v>
       </c>
@@ -6763,7 +6836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="10" t="s">
         <v>182</v>
       </c>
@@ -6780,7 +6853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="10" t="s">
         <v>174</v>
       </c>
@@ -6797,7 +6870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="10" t="s">
         <v>138</v>
       </c>
@@ -6814,7 +6887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="10" t="s">
         <v>331</v>
       </c>
@@ -6831,7 +6904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="10" t="s">
         <v>332</v>
       </c>
@@ -6848,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="10" t="s">
         <v>329</v>
       </c>
@@ -6865,7 +6938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="10" t="s">
         <v>330</v>
       </c>
@@ -6882,7 +6955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="10" t="s">
         <v>185</v>
       </c>
@@ -6899,7 +6972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="10" t="s">
         <v>203</v>
       </c>
@@ -6916,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="10" t="s">
         <v>200</v>
       </c>
@@ -6933,7 +7006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="10" t="s">
         <v>204</v>
       </c>
@@ -6950,7 +7023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="10" t="s">
         <v>163</v>
       </c>
@@ -6967,7 +7040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="10" t="s">
         <v>146</v>
       </c>
@@ -6984,7 +7057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="10" t="s">
         <v>202</v>
       </c>
@@ -7001,7 +7074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="10" t="s">
         <v>169</v>
       </c>
@@ -7018,7 +7091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="10" t="s">
         <v>160</v>
       </c>
@@ -7035,7 +7108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="10" t="s">
         <v>218</v>
       </c>
@@ -7052,7 +7125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="10" t="s">
         <v>158</v>
       </c>
@@ -7069,7 +7142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="10" t="s">
         <v>207</v>
       </c>
@@ -7086,7 +7159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="10" t="s">
         <v>184</v>
       </c>
@@ -7103,7 +7176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="10" t="s">
         <v>168</v>
       </c>
@@ -7120,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="10" t="s">
         <v>196</v>
       </c>
@@ -7137,7 +7210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="10" t="s">
         <v>210</v>
       </c>
@@ -7154,7 +7227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="10" t="s">
         <v>159</v>
       </c>
@@ -7171,7 +7244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="10" t="s">
         <v>167</v>
       </c>
@@ -7188,7 +7261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="10" t="s">
         <v>191</v>
       </c>
@@ -7205,7 +7278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
         <v>154</v>
       </c>
@@ -7222,7 +7295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="10" t="s">
         <v>227</v>
       </c>
@@ -7239,7 +7312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
         <v>222</v>
       </c>
@@ -7256,7 +7329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="10" t="s">
         <v>205</v>
       </c>
@@ -7273,7 +7346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="10" t="s">
         <v>176</v>
       </c>
@@ -7290,7 +7363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="10" t="s">
         <v>148</v>
       </c>
@@ -7307,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="10" t="s">
         <v>223</v>
       </c>
@@ -7324,7 +7397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="10" t="s">
         <v>145</v>
       </c>
@@ -7341,7 +7414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="10" t="s">
         <v>214</v>
       </c>
@@ -7358,7 +7431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="10" t="s">
         <v>228</v>
       </c>
@@ -7375,7 +7448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="10" t="s">
         <v>147</v>
       </c>
@@ -7392,7 +7465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="10" t="s">
         <v>142</v>
       </c>
@@ -7409,7 +7482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="10" t="s">
         <v>58</v>
       </c>
@@ -7426,7 +7499,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="10" t="s">
         <v>40</v>
       </c>
@@ -7443,7 +7516,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="10" t="s">
         <v>363</v>
       </c>
@@ -7460,7 +7533,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="10" t="s">
         <v>364</v>
       </c>
@@ -7477,7 +7550,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="10" t="s">
         <v>379</v>
       </c>
@@ -7494,7 +7567,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="10" t="s">
         <v>77</v>
       </c>
@@ -7511,7 +7584,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="10" t="s">
         <v>386</v>
       </c>
@@ -7528,7 +7601,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="10" t="s">
         <v>72</v>
       </c>
@@ -7545,7 +7618,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="10" t="s">
         <v>61</v>
       </c>
@@ -7562,7 +7635,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="10" t="s">
         <v>382</v>
       </c>
@@ -7579,7 +7652,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="10" t="s">
         <v>385</v>
       </c>
@@ -7596,7 +7669,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="10" t="s">
         <v>365</v>
       </c>
@@ -7613,7 +7686,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="10" t="s">
         <v>30</v>
       </c>
@@ -7630,7 +7703,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="10" t="s">
         <v>366</v>
       </c>
@@ -7647,7 +7720,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="10" t="s">
         <v>52</v>
       </c>
@@ -7664,7 +7737,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="10" t="s">
         <v>393</v>
       </c>
@@ -7681,7 +7754,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="10" t="s">
         <v>367</v>
       </c>
@@ -7698,7 +7771,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="10" t="s">
         <v>80</v>
       </c>
@@ -7715,7 +7788,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="10" t="s">
         <v>368</v>
       </c>
@@ -7732,7 +7805,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="10" t="s">
         <v>381</v>
       </c>
@@ -7749,7 +7822,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="10" t="s">
         <v>369</v>
       </c>
@@ -7766,7 +7839,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="10" t="s">
         <v>370</v>
       </c>
@@ -7783,7 +7856,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="10" t="s">
         <v>371</v>
       </c>
@@ -7800,7 +7873,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="10" t="s">
         <v>79</v>
       </c>
@@ -7817,7 +7890,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="10" t="s">
         <v>390</v>
       </c>
@@ -7834,7 +7907,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="10" t="s">
         <v>396</v>
       </c>
@@ -7851,7 +7924,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="10" t="s">
         <v>392</v>
       </c>
@@ -7868,7 +7941,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="10" t="s">
         <v>380</v>
       </c>
@@ -7885,7 +7958,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="10" t="s">
         <v>56</v>
       </c>
@@ -7902,7 +7975,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="10" t="s">
         <v>394</v>
       </c>
@@ -7919,7 +7992,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="10" t="s">
         <v>372</v>
       </c>
@@ -7936,7 +8009,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="10" t="s">
         <v>389</v>
       </c>
@@ -7953,7 +8026,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="10" t="s">
         <v>62</v>
       </c>
@@ -7970,7 +8043,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="10" t="s">
         <v>35</v>
       </c>
@@ -7987,7 +8060,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="10" t="s">
         <v>373</v>
       </c>
@@ -8004,7 +8077,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="10" t="s">
         <v>374</v>
       </c>
@@ -8021,7 +8094,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="10" t="s">
         <v>395</v>
       </c>
@@ -8038,7 +8111,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="10" t="s">
         <v>391</v>
       </c>
@@ -8055,7 +8128,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="10" t="s">
         <v>53</v>
       </c>
@@ -8072,7 +8145,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="10" t="s">
         <v>375</v>
       </c>
@@ -8089,7 +8162,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="10" t="s">
         <v>37</v>
       </c>
@@ -8106,7 +8179,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="10" t="s">
         <v>23</v>
       </c>
@@ -8123,7 +8196,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="10" t="s">
         <v>376</v>
       </c>
@@ -8140,7 +8213,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="10" t="s">
         <v>377</v>
       </c>
@@ -8157,7 +8230,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="10" t="s">
         <v>378</v>
       </c>
@@ -8174,28 +8247,419 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="16" t="s">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A366" s="16" t="s">
         <v>434</v>
       </c>
-      <c r="B367" s="16" t="s">
+      <c r="B366" s="16" t="s">
         <v>432</v>
       </c>
+      <c r="C366" s="17">
+        <v>20</v>
+      </c>
+      <c r="D366" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E366" s="19">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A367" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B367" s="20" t="s">
+        <v>83</v>
+      </c>
       <c r="C367" s="17">
         <v>20</v>
       </c>
-      <c r="D367" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E367" s="19">
+      <c r="D367" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E367" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A368" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="B368" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="C368" s="17">
+        <v>20</v>
+      </c>
+      <c r="D368" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E368" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A369" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B369" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="C369" s="17">
+        <v>20</v>
+      </c>
+      <c r="D369" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E369" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A370" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="B370" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="C370" s="17">
+        <v>20</v>
+      </c>
+      <c r="D370" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E370" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A371" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="B371" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="C371" s="17">
+        <v>20</v>
+      </c>
+      <c r="D371" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E371" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A372" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="B372" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="C372" s="17">
+        <v>20</v>
+      </c>
+      <c r="D372" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E372" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A373" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="B373" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="C373" s="17">
+        <v>20</v>
+      </c>
+      <c r="D373" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E373" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A374" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="B374" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="C374" s="17">
+        <v>20</v>
+      </c>
+      <c r="D374" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E374" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A375" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="B375" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="C375" s="17">
+        <v>20</v>
+      </c>
+      <c r="D375" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E375" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A376" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="B376" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="C376" s="17">
+        <v>20</v>
+      </c>
+      <c r="D376" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E376" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A377" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="B377" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="C377" s="17">
+        <v>20</v>
+      </c>
+      <c r="D377" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E377" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A378" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="B378" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="C378" s="17">
+        <v>20</v>
+      </c>
+      <c r="D378" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E378" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A379" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="B379" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="C379" s="17">
+        <v>20</v>
+      </c>
+      <c r="D379" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E379" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A380" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="B380" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="C380" s="17">
+        <v>20</v>
+      </c>
+      <c r="D380" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="E380" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A381" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="B381" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="C381" s="17">
+        <v>20</v>
+      </c>
+      <c r="D381" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E381" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A382" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="B382" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="C382" s="17">
+        <v>20</v>
+      </c>
+      <c r="D382" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E382" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A383" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="B383" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="C383" s="17">
+        <v>20</v>
+      </c>
+      <c r="D383" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E383" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A384" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B384" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="C384" s="17">
+        <v>20</v>
+      </c>
+      <c r="D384" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E384" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A385" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="B385" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="C385" s="17">
+        <v>20</v>
+      </c>
+      <c r="D385" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E385" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A386" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="B386" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="C386" s="17">
+        <v>20</v>
+      </c>
+      <c r="D386" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E386" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A387" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="B387" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="C387" s="17">
+        <v>20</v>
+      </c>
+      <c r="D387" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E387" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A388" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="B388" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="C388" s="17">
+        <v>20</v>
+      </c>
+      <c r="D388" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E388" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A389" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="B389" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="C389" s="17">
+        <v>20</v>
+      </c>
+      <c r="D389" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E389" s="19">
         <v>0.75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BFE381-CC10-44E9-891D-7E1894958B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4751B7-1200-4E81-8587-D0BFCA1007F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="462">
   <si>
     <t>Realizado_por</t>
   </si>
@@ -1410,6 +1410,18 @@
   </si>
   <si>
     <t>SONEL</t>
+  </si>
+  <si>
+    <t>HHR-EDO</t>
+  </si>
+  <si>
+    <t>HHR-JAME</t>
+  </si>
+  <si>
+    <t>HHR-LINCY</t>
+  </si>
+  <si>
+    <t>MB-ARCH</t>
   </si>
 </sst>
 </file>
@@ -1472,7 +1484,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1523,11 +1535,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1577,6 +1617,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1722,8 +1768,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E389" totalsRowShown="0">
-  <autoFilter ref="A1:E389" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E393" totalsRowShown="0">
+  <autoFilter ref="A1:E393" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E365">
     <sortCondition ref="A1:A365"/>
   </sortState>
@@ -2035,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD67F592-4C9C-4072-A458-8E5A8476F407}">
-  <dimension ref="A1:E389"/>
+  <dimension ref="A1:E393"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="53.77734375" customWidth="1"/>
@@ -8652,6 +8698,74 @@
         <v>24</v>
       </c>
       <c r="E389" s="19">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A390" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="B390" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="C390" s="13">
+        <v>20</v>
+      </c>
+      <c r="D390" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E390" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A391" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="B391" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="C391" s="13">
+        <v>20</v>
+      </c>
+      <c r="D391" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E391" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A392" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="B392" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="C392" s="13">
+        <v>20</v>
+      </c>
+      <c r="D392" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E392" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A393" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="B393" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="C393" s="17">
+        <v>0</v>
+      </c>
+      <c r="D393" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E393" s="19">
         <v>0.75</v>
       </c>
     </row>

--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4751B7-1200-4E81-8587-D0BFCA1007F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A65D8E5-B7B3-4566-93B0-4FE1F99772FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="472">
   <si>
     <t>Realizado_por</t>
   </si>
@@ -1422,13 +1422,43 @@
   </si>
   <si>
     <t>MB-ARCH</t>
+  </si>
+  <si>
+    <t>MB-INACIA</t>
+  </si>
+  <si>
+    <t>HMA-OCTO</t>
+  </si>
+  <si>
+    <t>HMA-PHILIP</t>
+  </si>
+  <si>
+    <t>HMA-WIDEL</t>
+  </si>
+  <si>
+    <t>MB-CASIMIR</t>
+  </si>
+  <si>
+    <t>MB-WILLIO</t>
+  </si>
+  <si>
+    <t>MB-KELLY</t>
+  </si>
+  <si>
+    <t>HFR-NISTRA</t>
+  </si>
+  <si>
+    <t>HMA-PARMIL</t>
+  </si>
+  <si>
+    <t>MB-VANESSA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1468,6 +1498,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1567,7 +1604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1623,6 +1660,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1768,8 +1811,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E393" totalsRowShown="0">
-  <autoFilter ref="A1:E393" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E403" totalsRowShown="0">
+  <autoFilter ref="A1:E403" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E365">
     <sortCondition ref="A1:A365"/>
   </sortState>
@@ -2081,7 +2124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD67F592-4C9C-4072-A458-8E5A8476F407}">
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="53.77734375" customWidth="1"/>
@@ -8652,78 +8695,72 @@
     </row>
     <row r="387" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A387" s="20" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B387" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="C387" s="17">
-        <v>20</v>
-      </c>
-      <c r="D387" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E387" s="8">
-        <v>0</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C387" s="13"/>
+      <c r="D387" s="9"/>
+      <c r="E387" s="8"/>
     </row>
     <row r="388" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A388" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="B388" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="C388" s="17">
+        <v>20</v>
+      </c>
+      <c r="D388" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E388" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A389" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="B388" s="20" t="s">
+      <c r="B389" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="C388" s="17">
-        <v>20</v>
-      </c>
-      <c r="D388" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E388" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A389" s="21" t="s">
+      <c r="C389" s="17">
+        <v>20</v>
+      </c>
+      <c r="D389" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E389" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A390" s="21" t="s">
         <v>456</v>
       </c>
-      <c r="B389" s="21" t="s">
+      <c r="B390" s="21" t="s">
         <v>456</v>
       </c>
-      <c r="C389" s="17">
-        <v>20</v>
-      </c>
-      <c r="D389" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E389" s="19">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A390" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="B390" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="C390" s="13">
-        <v>20</v>
-      </c>
-      <c r="D390" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E390" s="8">
+      <c r="C390" s="17">
+        <v>20</v>
+      </c>
+      <c r="D390" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E390" s="19">
         <v>0.75</v>
       </c>
     </row>
     <row r="391" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A391" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="B391" s="23" t="s">
-        <v>459</v>
+        <v>458</v>
+      </c>
+      <c r="B391" s="22" t="s">
+        <v>458</v>
       </c>
       <c r="C391" s="13">
         <v>20</v>
@@ -8737,37 +8774,191 @@
     </row>
     <row r="392" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A392" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="B392" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="C392" s="13">
+        <v>20</v>
+      </c>
+      <c r="D392" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E392" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A393" s="20" t="s">
         <v>460</v>
       </c>
-      <c r="B392" s="23" t="s">
+      <c r="B393" s="23" t="s">
         <v>460</v>
       </c>
-      <c r="C392" s="13">
-        <v>20</v>
-      </c>
-      <c r="D392" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E392" s="8">
+      <c r="C393" s="13">
+        <v>20</v>
+      </c>
+      <c r="D393" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E393" s="8">
         <v>0.7</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A393" s="21" t="s">
+    <row r="394" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A394" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="B393" s="23" t="s">
+      <c r="B394" s="23" t="s">
         <v>461</v>
       </c>
-      <c r="C393" s="17">
-        <v>0</v>
-      </c>
-      <c r="D393" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E393" s="19">
-        <v>0.75</v>
-      </c>
+      <c r="C394" s="17">
+        <v>0</v>
+      </c>
+      <c r="D394" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E394" s="19">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A395" s="24" t="s">
+        <v>462</v>
+      </c>
+      <c r="B395" s="24" t="s">
+        <v>462</v>
+      </c>
+      <c r="C395" s="13">
+        <v>20</v>
+      </c>
+      <c r="D395" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E395" s="8"/>
+    </row>
+    <row r="396" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A396" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="B396" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="C396" s="13">
+        <v>20</v>
+      </c>
+      <c r="D396" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E396" s="8"/>
+    </row>
+    <row r="397" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A397" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="B397" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="C397" s="13">
+        <v>20</v>
+      </c>
+      <c r="D397" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E397" s="8"/>
+    </row>
+    <row r="398" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A398" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="B398" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="C398" s="17">
+        <v>20</v>
+      </c>
+      <c r="D398" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E398" s="19"/>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A399" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="B399" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="C399" s="17">
+        <v>20</v>
+      </c>
+      <c r="D399" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E399" s="19"/>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A400" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="B400" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="C400" s="17">
+        <v>20</v>
+      </c>
+      <c r="D400" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E400" s="19"/>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A401" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="B401" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="C401" s="17">
+        <v>20</v>
+      </c>
+      <c r="D401" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E401" s="19"/>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A402" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="B402" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="C402" s="17">
+        <v>20</v>
+      </c>
+      <c r="D402" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E402" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A403" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="B403" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="C403" s="17">
+        <v>20</v>
+      </c>
+      <c r="D403" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E403" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/regras_milanov.xlsx
+++ b/regras_milanov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre Milanov\Desktop\COMPLIANCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A65D8E5-B7B3-4566-93B0-4FE1F99772FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE271BD-5883-4488-B410-01A29AE02FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0807A03-AAD5-4AB7-8E66-5C56774828CB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="480">
   <si>
     <t>Realizado_por</t>
   </si>
@@ -1452,6 +1452,30 @@
   </si>
   <si>
     <t>MB-VANESSA</t>
+  </si>
+  <si>
+    <t>HFR-CHRIS</t>
+  </si>
+  <si>
+    <t>HHR-RUBEN</t>
+  </si>
+  <si>
+    <t>HMA-LAMY</t>
+  </si>
+  <si>
+    <t>HRE-ASNEL</t>
+  </si>
+  <si>
+    <t>HSO-JUREL</t>
+  </si>
+  <si>
+    <t>MB-QUESSA</t>
+  </si>
+  <si>
+    <t>MB-SAINT</t>
+  </si>
+  <si>
+    <t>MB-SOMMER</t>
   </si>
 </sst>
 </file>
@@ -1811,8 +1835,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E403" totalsRowShown="0">
-  <autoFilter ref="A1:E403" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}" name="Tabela1" displayName="Tabela1" ref="A1:E411" totalsRowShown="0">
+  <autoFilter ref="A1:E411" xr:uid="{6B430856-6922-4FD4-BBB1-92ED3421B23F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E365">
     <sortCondition ref="A1:A365"/>
   </sortState>
@@ -2124,7 +2148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD67F592-4C9C-4072-A458-8E5A8476F407}">
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="53.77734375" customWidth="1"/>
@@ -8960,9 +8984,129 @@
       </c>
       <c r="E403" s="19"/>
     </row>
+    <row r="404" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A404" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="B404" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="C404" s="13">
+        <v>20</v>
+      </c>
+      <c r="D404" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E404" s="8"/>
+    </row>
+    <row r="405" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A405" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="B405" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="C405" s="13">
+        <v>20</v>
+      </c>
+      <c r="D405" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E405" s="8"/>
+    </row>
+    <row r="406" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A406" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="B406" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="C406" s="13">
+        <v>20</v>
+      </c>
+      <c r="D406" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E406" s="8"/>
+    </row>
+    <row r="407" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A407" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="B407" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="C407" s="13">
+        <v>20</v>
+      </c>
+      <c r="D407" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E407" s="8"/>
+    </row>
+    <row r="408" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A408" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="B408" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="C408" s="13">
+        <v>20</v>
+      </c>
+      <c r="D408" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E408" s="8"/>
+    </row>
+    <row r="409" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A409" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="B409" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="C409" s="13">
+        <v>20</v>
+      </c>
+      <c r="D409" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E409" s="8"/>
+    </row>
+    <row r="410" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A410" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="B410" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="C410" s="13">
+        <v>20</v>
+      </c>
+      <c r="D410" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E410" s="8"/>
+    </row>
+    <row r="411" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A411" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="B411" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C411" s="17">
+        <v>20</v>
+      </c>
+      <c r="D411" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E411" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
